--- a/4_output_anylogic/forecast_combined.xlsx
+++ b/4_output_anylogic/forecast_combined.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F121"/>
+  <dimension ref="A1:B121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,45 +434,13 @@
           <t>forecast</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ci80_lower</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>ci80_upper</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>ci95_lower</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>ci95_upper</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>14486.87801945044</v>
-      </c>
-      <c r="C2" t="n">
-        <v>4089.40398367631</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24884.35205522458</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-1434.254097828698</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30408.01013672959</v>
+        <v>8098.062949874969</v>
       </c>
     </row>
     <row r="3">
@@ -480,19 +448,7 @@
         <v>46054</v>
       </c>
       <c r="B3" t="n">
-        <v>13365.62167916006</v>
-      </c>
-      <c r="C3" t="n">
-        <v>2968.147643385924</v>
-      </c>
-      <c r="D3" t="n">
-        <v>23763.09571493419</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-2555.510438119083</v>
-      </c>
-      <c r="F3" t="n">
-        <v>29286.7537964392</v>
+        <v>8389.50219373759</v>
       </c>
     </row>
     <row r="4">
@@ -500,19 +456,7 @@
         <v>46082</v>
       </c>
       <c r="B4" t="n">
-        <v>14616.77258664272</v>
-      </c>
-      <c r="C4" t="n">
-        <v>4219.298550868585</v>
-      </c>
-      <c r="D4" t="n">
-        <v>25014.24662241685</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-1304.359530636422</v>
-      </c>
-      <c r="F4" t="n">
-        <v>30537.90470392186</v>
+        <v>8551.459769661642</v>
       </c>
     </row>
     <row r="5">
@@ -520,19 +464,7 @@
         <v>46113</v>
       </c>
       <c r="B5" t="n">
-        <v>14862.47726793582</v>
-      </c>
-      <c r="C5" t="n">
-        <v>4465.003232161689</v>
-      </c>
-      <c r="D5" t="n">
-        <v>25259.95130370996</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-1058.654849343318</v>
-      </c>
-      <c r="F5" t="n">
-        <v>30783.60938521496</v>
+        <v>9983.520662208812</v>
       </c>
     </row>
     <row r="6">
@@ -540,19 +472,7 @@
         <v>46143</v>
       </c>
       <c r="B6" t="n">
-        <v>18462.05986696059</v>
-      </c>
-      <c r="C6" t="n">
-        <v>8064.585831186456</v>
-      </c>
-      <c r="D6" t="n">
-        <v>28859.53390273472</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2540.927749681448</v>
-      </c>
-      <c r="F6" t="n">
-        <v>34383.19198423973</v>
+        <v>11266.7627717287</v>
       </c>
     </row>
     <row r="7">
@@ -560,19 +480,7 @@
         <v>46174</v>
       </c>
       <c r="B7" t="n">
-        <v>23193.33704792635</v>
-      </c>
-      <c r="C7" t="n">
-        <v>12795.86301215221</v>
-      </c>
-      <c r="D7" t="n">
-        <v>33590.81108370048</v>
-      </c>
-      <c r="E7" t="n">
-        <v>7272.204930647205</v>
-      </c>
-      <c r="F7" t="n">
-        <v>39114.46916520549</v>
+        <v>9521.209191800013</v>
       </c>
     </row>
     <row r="8">
@@ -580,19 +488,7 @@
         <v>46204</v>
       </c>
       <c r="B8" t="n">
-        <v>16672.05188374761</v>
-      </c>
-      <c r="C8" t="n">
-        <v>6274.577847973474</v>
-      </c>
-      <c r="D8" t="n">
-        <v>27069.52591952174</v>
-      </c>
-      <c r="E8" t="n">
-        <v>750.9197664684671</v>
-      </c>
-      <c r="F8" t="n">
-        <v>32593.18400102675</v>
+        <v>9376.67196674421</v>
       </c>
     </row>
     <row r="9">
@@ -600,19 +496,7 @@
         <v>46235</v>
       </c>
       <c r="B9" t="n">
-        <v>16662.64491775702</v>
-      </c>
-      <c r="C9" t="n">
-        <v>6265.170881982884</v>
-      </c>
-      <c r="D9" t="n">
-        <v>27060.11895353115</v>
-      </c>
-      <c r="E9" t="n">
-        <v>741.5128004778762</v>
-      </c>
-      <c r="F9" t="n">
-        <v>32583.77703503616</v>
+        <v>8980.320892368351</v>
       </c>
     </row>
     <row r="10">
@@ -620,19 +504,7 @@
         <v>46266</v>
       </c>
       <c r="B10" t="n">
-        <v>13704.31562615442</v>
-      </c>
-      <c r="C10" t="n">
-        <v>3306.841590380289</v>
-      </c>
-      <c r="D10" t="n">
-        <v>24101.78966192856</v>
-      </c>
-      <c r="E10" t="n">
-        <v>-2216.816491124719</v>
-      </c>
-      <c r="F10" t="n">
-        <v>29625.44774343356</v>
+        <v>7898.699325736817</v>
       </c>
     </row>
     <row r="11">
@@ -640,19 +512,7 @@
         <v>46296</v>
       </c>
       <c r="B11" t="n">
-        <v>19226.10711191848</v>
-      </c>
-      <c r="C11" t="n">
-        <v>8828.633076144344</v>
-      </c>
-      <c r="D11" t="n">
-        <v>29623.58114769261</v>
-      </c>
-      <c r="E11" t="n">
-        <v>3304.974994639337</v>
-      </c>
-      <c r="F11" t="n">
-        <v>35147.23922919762</v>
+        <v>10166.37620582466</v>
       </c>
     </row>
     <row r="12">
@@ -660,19 +520,7 @@
         <v>46327</v>
       </c>
       <c r="B12" t="n">
-        <v>15109.49346284714</v>
-      </c>
-      <c r="C12" t="n">
-        <v>4712.019427073003</v>
-      </c>
-      <c r="D12" t="n">
-        <v>25506.96749862127</v>
-      </c>
-      <c r="E12" t="n">
-        <v>-811.6386544320048</v>
-      </c>
-      <c r="F12" t="n">
-        <v>31030.62558012628</v>
+        <v>8433.554756832091</v>
       </c>
     </row>
     <row r="13">
@@ -680,19 +528,7 @@
         <v>46357</v>
       </c>
       <c r="B13" t="n">
-        <v>15619.3774156327</v>
-      </c>
-      <c r="C13" t="n">
-        <v>5221.903379858564</v>
-      </c>
-      <c r="D13" t="n">
-        <v>26016.85145140683</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-301.7547016464432</v>
-      </c>
-      <c r="F13" t="n">
-        <v>31540.50953291184</v>
+        <v>9089.040513846723</v>
       </c>
     </row>
     <row r="14">
@@ -700,19 +536,7 @@
         <v>46388</v>
       </c>
       <c r="B14" t="n">
-        <v>15314.7673172785</v>
-      </c>
-      <c r="C14" t="n">
-        <v>4917.293281504362</v>
-      </c>
-      <c r="D14" t="n">
-        <v>25712.24135305263</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-606.3648000006451</v>
-      </c>
-      <c r="F14" t="n">
-        <v>31235.89943455764</v>
+        <v>8549.578014743205</v>
       </c>
     </row>
     <row r="15">
@@ -720,19 +544,7 @@
         <v>46419</v>
       </c>
       <c r="B15" t="n">
-        <v>14125.8136885406</v>
-      </c>
-      <c r="C15" t="n">
-        <v>3728.339652766464</v>
-      </c>
-      <c r="D15" t="n">
-        <v>24523.28772431473</v>
-      </c>
-      <c r="E15" t="n">
-        <v>-1795.318428738543</v>
-      </c>
-      <c r="F15" t="n">
-        <v>30046.94580581974</v>
+        <v>8955.235251202406</v>
       </c>
     </row>
     <row r="16">
@@ -740,19 +552,7 @@
         <v>46447</v>
       </c>
       <c r="B16" t="n">
-        <v>15444.20409366691</v>
-      </c>
-      <c r="C16" t="n">
-        <v>5046.730057892772</v>
-      </c>
-      <c r="D16" t="n">
-        <v>25841.67812944104</v>
-      </c>
-      <c r="E16" t="n">
-        <v>-476.9280236122358</v>
-      </c>
-      <c r="F16" t="n">
-        <v>31365.33621094605</v>
+        <v>9071.497250258626</v>
       </c>
     </row>
     <row r="17">
@@ -760,19 +560,7 @@
         <v>46478</v>
       </c>
       <c r="B17" t="n">
-        <v>15699.86744010663</v>
-      </c>
-      <c r="C17" t="n">
-        <v>5302.393404332497</v>
-      </c>
-      <c r="D17" t="n">
-        <v>26097.34147588076</v>
-      </c>
-      <c r="E17" t="n">
-        <v>-221.2646771725103</v>
-      </c>
-      <c r="F17" t="n">
-        <v>31620.99955738577</v>
+        <v>10621.41590180386</v>
       </c>
     </row>
     <row r="18">
@@ -780,19 +568,7 @@
         <v>46508</v>
       </c>
       <c r="B18" t="n">
-        <v>19497.39863791906</v>
-      </c>
-      <c r="C18" t="n">
-        <v>9099.924602144927</v>
-      </c>
-      <c r="D18" t="n">
-        <v>29894.87267369319</v>
-      </c>
-      <c r="E18" t="n">
-        <v>3576.26652063992</v>
-      </c>
-      <c r="F18" t="n">
-        <v>35418.5307551982</v>
+        <v>11958.03896760601</v>
       </c>
     </row>
     <row r="19">
@@ -800,19 +576,7 @@
         <v>46539</v>
       </c>
       <c r="B19" t="n">
-        <v>24487.95228228949</v>
-      </c>
-      <c r="C19" t="n">
-        <v>14090.47824651535</v>
-      </c>
-      <c r="D19" t="n">
-        <v>34885.42631806362</v>
-      </c>
-      <c r="E19" t="n">
-        <v>8566.820165010346</v>
-      </c>
-      <c r="F19" t="n">
-        <v>40409.08439956863</v>
+        <v>10076.00199621444</v>
       </c>
     </row>
     <row r="20">
@@ -820,19 +584,7 @@
         <v>46569</v>
       </c>
       <c r="B20" t="n">
-        <v>17598.35062809094</v>
-      </c>
-      <c r="C20" t="n">
-        <v>7200.876592316805</v>
-      </c>
-      <c r="D20" t="n">
-        <v>27995.82466386507</v>
-      </c>
-      <c r="E20" t="n">
-        <v>1677.218510811797</v>
-      </c>
-      <c r="F20" t="n">
-        <v>33519.48274537008</v>
+        <v>9831.398758643378</v>
       </c>
     </row>
     <row r="21">
@@ -840,19 +592,7 @@
         <v>46600</v>
       </c>
       <c r="B21" t="n">
-        <v>17584.15442442368</v>
-      </c>
-      <c r="C21" t="n">
-        <v>7186.680388649545</v>
-      </c>
-      <c r="D21" t="n">
-        <v>27981.62846019781</v>
-      </c>
-      <c r="E21" t="n">
-        <v>1663.022307144538</v>
-      </c>
-      <c r="F21" t="n">
-        <v>33505.28654170282</v>
+        <v>9415.961869327006</v>
       </c>
     </row>
     <row r="22">
@@ -860,19 +600,7 @@
         <v>46631</v>
       </c>
       <c r="B22" t="n">
-        <v>14458.7410496445</v>
-      </c>
-      <c r="C22" t="n">
-        <v>4061.267013870371</v>
-      </c>
-      <c r="D22" t="n">
-        <v>24856.21508541864</v>
-      </c>
-      <c r="E22" t="n">
-        <v>-1462.391067634637</v>
-      </c>
-      <c r="F22" t="n">
-        <v>30379.87316692364</v>
+        <v>8345.307420822233</v>
       </c>
     </row>
     <row r="23">
@@ -880,19 +608,7 @@
         <v>46661</v>
       </c>
       <c r="B23" t="n">
-        <v>20279.6750432027</v>
-      </c>
-      <c r="C23" t="n">
-        <v>9882.201007428566</v>
-      </c>
-      <c r="D23" t="n">
-        <v>30677.14907897684</v>
-      </c>
-      <c r="E23" t="n">
-        <v>4358.542925923559</v>
-      </c>
-      <c r="F23" t="n">
-        <v>36200.80716048184</v>
+        <v>10764.89875668601</v>
       </c>
     </row>
     <row r="24">
@@ -900,19 +616,7 @@
         <v>46692</v>
       </c>
       <c r="B24" t="n">
-        <v>15933.7119848062</v>
-      </c>
-      <c r="C24" t="n">
-        <v>5536.237949032069</v>
-      </c>
-      <c r="D24" t="n">
-        <v>26331.18602058034</v>
-      </c>
-      <c r="E24" t="n">
-        <v>12.57986752706165</v>
-      </c>
-      <c r="F24" t="n">
-        <v>31854.84410208534</v>
+        <v>8942.822488268292</v>
       </c>
     </row>
     <row r="25">
@@ -920,19 +624,7 @@
         <v>46722</v>
       </c>
       <c r="B25" t="n">
-        <v>16467.55431007467</v>
-      </c>
-      <c r="C25" t="n">
-        <v>6070.080274300532</v>
-      </c>
-      <c r="D25" t="n">
-        <v>26865.0283458488</v>
-      </c>
-      <c r="E25" t="n">
-        <v>546.4221927955241</v>
-      </c>
-      <c r="F25" t="n">
-        <v>32388.68642735381</v>
+        <v>9647.567369607657</v>
       </c>
     </row>
     <row r="26">
@@ -940,19 +632,7 @@
         <v>46753</v>
       </c>
       <c r="B26" t="n">
-        <v>16142.65661510655</v>
-      </c>
-      <c r="C26" t="n">
-        <v>5745.182579332413</v>
-      </c>
-      <c r="D26" t="n">
-        <v>26540.13065088068</v>
-      </c>
-      <c r="E26" t="n">
-        <v>221.5244978274059</v>
-      </c>
-      <c r="F26" t="n">
-        <v>32063.78873238569</v>
+        <v>9080.850814583739</v>
       </c>
     </row>
     <row r="27">
@@ -960,19 +640,7 @@
         <v>46784</v>
       </c>
       <c r="B27" t="n">
-        <v>14886.00569792114</v>
-      </c>
-      <c r="C27" t="n">
-        <v>4488.531662147005</v>
-      </c>
-      <c r="D27" t="n">
-        <v>25283.47973369527</v>
-      </c>
-      <c r="E27" t="n">
-        <v>-1035.126419358003</v>
-      </c>
-      <c r="F27" t="n">
-        <v>30807.13781520028</v>
+        <v>9493.229017640133</v>
       </c>
     </row>
     <row r="28">
@@ -980,19 +648,7 @@
         <v>46813</v>
       </c>
       <c r="B28" t="n">
-        <v>16271.63560069109</v>
-      </c>
-      <c r="C28" t="n">
-        <v>5874.161564916956</v>
-      </c>
-      <c r="D28" t="n">
-        <v>26669.10963646523</v>
-      </c>
-      <c r="E28" t="n">
-        <v>350.5034834119488</v>
-      </c>
-      <c r="F28" t="n">
-        <v>32192.76771797023</v>
+        <v>9606.802136960492</v>
       </c>
     </row>
     <row r="29">
@@ -1000,19 +656,7 @@
         <v>46844</v>
       </c>
       <c r="B29" t="n">
-        <v>16537.25761227744</v>
-      </c>
-      <c r="C29" t="n">
-        <v>6139.783576503307</v>
-      </c>
-      <c r="D29" t="n">
-        <v>26934.73164805157</v>
-      </c>
-      <c r="E29" t="n">
-        <v>616.1254949982995</v>
-      </c>
-      <c r="F29" t="n">
-        <v>32458.38972955658</v>
+        <v>11163.65593106447</v>
       </c>
     </row>
     <row r="30">
@@ -1020,19 +664,7 @@
         <v>46874</v>
       </c>
       <c r="B30" t="n">
-        <v>20532.73740887753</v>
-      </c>
-      <c r="C30" t="n">
-        <v>10135.2633731034</v>
-      </c>
-      <c r="D30" t="n">
-        <v>30930.21144465166</v>
-      </c>
-      <c r="E30" t="n">
-        <v>4611.605291598391</v>
-      </c>
-      <c r="F30" t="n">
-        <v>36453.86952615668</v>
+        <v>12503.42010989036</v>
       </c>
     </row>
     <row r="31">
@@ -1040,19 +672,7 @@
         <v>46905</v>
       </c>
       <c r="B31" t="n">
-        <v>25782.56751665263</v>
-      </c>
-      <c r="C31" t="n">
-        <v>15385.09348087849</v>
-      </c>
-      <c r="D31" t="n">
-        <v>36180.04155242676</v>
-      </c>
-      <c r="E31" t="n">
-        <v>9861.435399373486</v>
-      </c>
-      <c r="F31" t="n">
-        <v>41703.69963393177</v>
+        <v>10613.35200177312</v>
       </c>
     </row>
     <row r="32">
@@ -1060,19 +680,7 @@
         <v>46935</v>
       </c>
       <c r="B32" t="n">
-        <v>18524.64937243427</v>
-      </c>
-      <c r="C32" t="n">
-        <v>8127.175336660135</v>
-      </c>
-      <c r="D32" t="n">
-        <v>28922.1234082084</v>
-      </c>
-      <c r="E32" t="n">
-        <v>2603.517255155128</v>
-      </c>
-      <c r="F32" t="n">
-        <v>34445.78148971341</v>
+        <v>10362.8605471854</v>
       </c>
     </row>
     <row r="33">
@@ -1080,19 +688,7 @@
         <v>46966</v>
       </c>
       <c r="B33" t="n">
-        <v>18505.66393109035</v>
-      </c>
-      <c r="C33" t="n">
-        <v>8108.189895316214</v>
-      </c>
-      <c r="D33" t="n">
-        <v>28903.13796686448</v>
-      </c>
-      <c r="E33" t="n">
-        <v>2584.531813811207</v>
-      </c>
-      <c r="F33" t="n">
-        <v>34426.79604836949</v>
+        <v>9946.300585034562</v>
       </c>
     </row>
     <row r="34">
@@ -1100,19 +696,7 @@
         <v>46997</v>
       </c>
       <c r="B34" t="n">
-        <v>15213.16647313459</v>
-      </c>
-      <c r="C34" t="n">
-        <v>4815.692437360454</v>
-      </c>
-      <c r="D34" t="n">
-        <v>25610.64050890872</v>
-      </c>
-      <c r="E34" t="n">
-        <v>-707.9656441445532</v>
-      </c>
-      <c r="F34" t="n">
-        <v>31134.29859041373</v>
+        <v>8876.291478239271</v>
       </c>
     </row>
     <row r="35">
@@ -1120,19 +704,7 @@
         <v>47027</v>
       </c>
       <c r="B35" t="n">
-        <v>21333.24297448693</v>
-      </c>
-      <c r="C35" t="n">
-        <v>10935.76893871279</v>
-      </c>
-      <c r="D35" t="n">
-        <v>31730.71701026106</v>
-      </c>
-      <c r="E35" t="n">
-        <v>5412.110857207785</v>
-      </c>
-      <c r="F35" t="n">
-        <v>37254.37509176607</v>
+        <v>11304.82196597981</v>
       </c>
     </row>
     <row r="36">
@@ -1140,19 +712,7 @@
         <v>47058</v>
       </c>
       <c r="B36" t="n">
-        <v>16757.93050676527</v>
-      </c>
-      <c r="C36" t="n">
-        <v>6360.456470991141</v>
-      </c>
-      <c r="D36" t="n">
-        <v>27155.40454253941</v>
-      </c>
-      <c r="E36" t="n">
-        <v>836.7983894861336</v>
-      </c>
-      <c r="F36" t="n">
-        <v>32679.06262404442</v>
+        <v>9477.493647107125</v>
       </c>
     </row>
     <row r="37">
@@ -1160,19 +720,7 @@
         <v>47088</v>
       </c>
       <c r="B37" t="n">
-        <v>17315.73120451663</v>
-      </c>
-      <c r="C37" t="n">
-        <v>6918.257168742499</v>
-      </c>
-      <c r="D37" t="n">
-        <v>27713.20524029076</v>
-      </c>
-      <c r="E37" t="n">
-        <v>1394.599087237491</v>
-      </c>
-      <c r="F37" t="n">
-        <v>33236.86332179578</v>
+        <v>10185.1370991678</v>
       </c>
     </row>
     <row r="38">
@@ -1180,19 +728,7 @@
         <v>47119</v>
       </c>
       <c r="B38" t="n">
-        <v>16970.5459129346</v>
-      </c>
-      <c r="C38" t="n">
-        <v>6573.071877160464</v>
-      </c>
-      <c r="D38" t="n">
-        <v>27368.01994870873</v>
-      </c>
-      <c r="E38" t="n">
-        <v>1049.413795655457</v>
-      </c>
-      <c r="F38" t="n">
-        <v>32891.67803021374</v>
+        <v>9616.816824840893</v>
       </c>
     </row>
     <row r="39">
@@ -1200,19 +736,7 @@
         <v>47150</v>
       </c>
       <c r="B39" t="n">
-        <v>15646.19770730168</v>
-      </c>
-      <c r="C39" t="n">
-        <v>5248.723671527545</v>
-      </c>
-      <c r="D39" t="n">
-        <v>26043.67174307581</v>
-      </c>
-      <c r="E39" t="n">
-        <v>-274.9344099774626</v>
-      </c>
-      <c r="F39" t="n">
-        <v>31567.32982458082</v>
+        <v>10029.59051192719</v>
       </c>
     </row>
     <row r="40">
@@ -1220,19 +744,7 @@
         <v>47178</v>
       </c>
       <c r="B40" t="n">
-        <v>17099.06710771528</v>
-      </c>
-      <c r="C40" t="n">
-        <v>6701.593071941146</v>
-      </c>
-      <c r="D40" t="n">
-        <v>27496.54114348941</v>
-      </c>
-      <c r="E40" t="n">
-        <v>1177.934990436139</v>
-      </c>
-      <c r="F40" t="n">
-        <v>33020.19922499442</v>
+        <v>10143.00540862012</v>
       </c>
     </row>
     <row r="41">
@@ -1240,19 +752,7 @@
         <v>47209</v>
       </c>
       <c r="B41" t="n">
-        <v>17374.64778444825</v>
-      </c>
-      <c r="C41" t="n">
-        <v>6977.173748674117</v>
-      </c>
-      <c r="D41" t="n">
-        <v>27772.12182022238</v>
-      </c>
-      <c r="E41" t="n">
-        <v>1453.515667169109</v>
-      </c>
-      <c r="F41" t="n">
-        <v>33295.77990172739</v>
+        <v>11700.26728957998</v>
       </c>
     </row>
     <row r="42">
@@ -1260,19 +760,7 @@
         <v>47239</v>
       </c>
       <c r="B42" t="n">
-        <v>21568.076179836</v>
-      </c>
-      <c r="C42" t="n">
-        <v>11170.60214406187</v>
-      </c>
-      <c r="D42" t="n">
-        <v>31965.55021561014</v>
-      </c>
-      <c r="E42" t="n">
-        <v>5646.944062556862</v>
-      </c>
-      <c r="F42" t="n">
-        <v>37489.20829711515</v>
+        <v>13040.21630194418</v>
       </c>
     </row>
     <row r="43">
@@ -1280,19 +768,7 @@
         <v>47270</v>
       </c>
       <c r="B43" t="n">
-        <v>27077.18275101577</v>
-      </c>
-      <c r="C43" t="n">
-        <v>16679.70871524164</v>
-      </c>
-      <c r="D43" t="n">
-        <v>37474.6567867899</v>
-      </c>
-      <c r="E43" t="n">
-        <v>11156.05063373663</v>
-      </c>
-      <c r="F43" t="n">
-        <v>42998.31486829491</v>
+        <v>11149.67561502878</v>
       </c>
     </row>
     <row r="44">
@@ -1300,19 +776,7 @@
         <v>47300</v>
       </c>
       <c r="B44" t="n">
-        <v>19450.9481167776</v>
-      </c>
-      <c r="C44" t="n">
-        <v>9053.474081003469</v>
-      </c>
-      <c r="D44" t="n">
-        <v>29848.42215255174</v>
-      </c>
-      <c r="E44" t="n">
-        <v>3529.815999498462</v>
-      </c>
-      <c r="F44" t="n">
-        <v>35372.08023405675</v>
+        <v>10898.83767816637</v>
       </c>
     </row>
     <row r="45">
@@ -1320,19 +784,7 @@
         <v>47331</v>
       </c>
       <c r="B45" t="n">
-        <v>19427.17343775701</v>
-      </c>
-      <c r="C45" t="n">
-        <v>9029.699401982876</v>
-      </c>
-      <c r="D45" t="n">
-        <v>29824.64747353114</v>
-      </c>
-      <c r="E45" t="n">
-        <v>3506.041320477869</v>
-      </c>
-      <c r="F45" t="n">
-        <v>35348.30555503615</v>
+        <v>10482.21163067437</v>
       </c>
     </row>
     <row r="46">
@@ -1340,19 +792,7 @@
         <v>47362</v>
       </c>
       <c r="B46" t="n">
-        <v>15967.59189662467</v>
-      </c>
-      <c r="C46" t="n">
-        <v>5570.117860850538</v>
-      </c>
-      <c r="D46" t="n">
-        <v>26365.06593239881</v>
-      </c>
-      <c r="E46" t="n">
-        <v>46.45977934553048</v>
-      </c>
-      <c r="F46" t="n">
-        <v>31888.72401390381</v>
+        <v>9412.240497931807</v>
       </c>
     </row>
     <row r="47">
@@ -1360,19 +800,7 @@
         <v>47392</v>
       </c>
       <c r="B47" t="n">
-        <v>22386.81090577115</v>
-      </c>
-      <c r="C47" t="n">
-        <v>11989.33686999701</v>
-      </c>
-      <c r="D47" t="n">
-        <v>32784.28494154528</v>
-      </c>
-      <c r="E47" t="n">
-        <v>6465.678788492007</v>
-      </c>
-      <c r="F47" t="n">
-        <v>38307.94302305029</v>
+        <v>11841.29699510225</v>
       </c>
     </row>
     <row r="48">
@@ -1380,19 +808,7 @@
         <v>47423</v>
       </c>
       <c r="B48" t="n">
-        <v>17582.14902872434</v>
-      </c>
-      <c r="C48" t="n">
-        <v>7184.674992950206</v>
-      </c>
-      <c r="D48" t="n">
-        <v>27979.62306449848</v>
-      </c>
-      <c r="E48" t="n">
-        <v>1661.016911445198</v>
-      </c>
-      <c r="F48" t="n">
-        <v>33503.28114600348</v>
+        <v>10013.65962811139</v>
       </c>
     </row>
     <row r="49">
@@ -1400,19 +816,7 @@
         <v>47453</v>
       </c>
       <c r="B49" t="n">
-        <v>18163.9080989586</v>
-      </c>
-      <c r="C49" t="n">
-        <v>7766.434063184466</v>
-      </c>
-      <c r="D49" t="n">
-        <v>28561.38213473273</v>
-      </c>
-      <c r="E49" t="n">
-        <v>2242.775981679459</v>
-      </c>
-      <c r="F49" t="n">
-        <v>34085.04021623774</v>
+        <v>10721.47364171455</v>
       </c>
     </row>
     <row r="50">
@@ -1420,19 +824,7 @@
         <v>47484</v>
       </c>
       <c r="B50" t="n">
-        <v>17798.43521076265</v>
-      </c>
-      <c r="C50" t="n">
-        <v>7400.961174988513</v>
-      </c>
-      <c r="D50" t="n">
-        <v>28195.90924653678</v>
-      </c>
-      <c r="E50" t="n">
-        <v>1877.303093483506</v>
-      </c>
-      <c r="F50" t="n">
-        <v>33719.56732804179</v>
+        <v>10153.05899920955</v>
       </c>
     </row>
     <row r="51">
@@ -1440,19 +832,7 @@
         <v>47515</v>
       </c>
       <c r="B51" t="n">
-        <v>16406.38971668222</v>
-      </c>
-      <c r="C51" t="n">
-        <v>6008.915680908087</v>
-      </c>
-      <c r="D51" t="n">
-        <v>26803.86375245635</v>
-      </c>
-      <c r="E51" t="n">
-        <v>485.2575994030794</v>
-      </c>
-      <c r="F51" t="n">
-        <v>32327.52183396136</v>
+        <v>10565.85595789163</v>
       </c>
     </row>
     <row r="52">
@@ -1460,19 +840,7 @@
         <v>47543</v>
       </c>
       <c r="B52" t="n">
-        <v>17926.49861473947</v>
-      </c>
-      <c r="C52" t="n">
-        <v>7529.024578965333</v>
-      </c>
-      <c r="D52" t="n">
-        <v>28323.9726505136</v>
-      </c>
-      <c r="E52" t="n">
-        <v>2005.366497460325</v>
-      </c>
-      <c r="F52" t="n">
-        <v>33847.63073201861</v>
+        <v>10679.26154423888</v>
       </c>
     </row>
     <row r="53">
@@ -1480,19 +848,7 @@
         <v>47574</v>
       </c>
       <c r="B53" t="n">
-        <v>18212.03795661906</v>
-      </c>
-      <c r="C53" t="n">
-        <v>7814.563920844923</v>
-      </c>
-      <c r="D53" t="n">
-        <v>28609.51199239319</v>
-      </c>
-      <c r="E53" t="n">
-        <v>2290.905839339915</v>
-      </c>
-      <c r="F53" t="n">
-        <v>34133.1700738982</v>
+        <v>12236.54743838671</v>
       </c>
     </row>
     <row r="54">
@@ -1500,19 +856,7 @@
         <v>47604</v>
       </c>
       <c r="B54" t="n">
-        <v>22603.41495079447</v>
-      </c>
-      <c r="C54" t="n">
-        <v>12205.94091502034</v>
-      </c>
-      <c r="D54" t="n">
-        <v>33000.88898656861</v>
-      </c>
-      <c r="E54" t="n">
-        <v>6682.282833515334</v>
-      </c>
-      <c r="F54" t="n">
-        <v>38524.54706807362</v>
+        <v>13576.50732697111</v>
       </c>
     </row>
     <row r="55">
@@ -1520,19 +864,7 @@
         <v>47635</v>
       </c>
       <c r="B55" t="n">
-        <v>28371.79798537891</v>
-      </c>
-      <c r="C55" t="n">
-        <v>17974.32394960478</v>
-      </c>
-      <c r="D55" t="n">
-        <v>38769.27202115304</v>
-      </c>
-      <c r="E55" t="n">
-        <v>12450.66586809977</v>
-      </c>
-      <c r="F55" t="n">
-        <v>44292.93010265805</v>
+        <v>11685.93883194733</v>
       </c>
     </row>
     <row r="56">
@@ -1540,19 +872,7 @@
         <v>47665</v>
       </c>
       <c r="B56" t="n">
-        <v>20377.24686112093</v>
-      </c>
-      <c r="C56" t="n">
-        <v>9979.772825346799</v>
-      </c>
-      <c r="D56" t="n">
-        <v>30774.72089689507</v>
-      </c>
-      <c r="E56" t="n">
-        <v>4456.114743841792</v>
-      </c>
-      <c r="F56" t="n">
-        <v>36298.37897840008</v>
+        <v>11435.0805069154</v>
       </c>
     </row>
     <row r="57">
@@ -1560,19 +880,7 @@
         <v>47696</v>
       </c>
       <c r="B57" t="n">
-        <v>20348.68294442368</v>
-      </c>
-      <c r="C57" t="n">
-        <v>9951.208908649542</v>
-      </c>
-      <c r="D57" t="n">
-        <v>30746.15698019781</v>
-      </c>
-      <c r="E57" t="n">
-        <v>4427.550827144534</v>
-      </c>
-      <c r="F57" t="n">
-        <v>36269.81506170282</v>
+        <v>11018.45057074212</v>
       </c>
     </row>
     <row r="58">
@@ -1580,19 +888,7 @@
         <v>47727</v>
       </c>
       <c r="B58" t="n">
-        <v>16722.01732011476</v>
-      </c>
-      <c r="C58" t="n">
-        <v>6324.543284340622</v>
-      </c>
-      <c r="D58" t="n">
-        <v>27119.49135588889</v>
-      </c>
-      <c r="E58" t="n">
-        <v>800.8852028356141</v>
-      </c>
-      <c r="F58" t="n">
-        <v>32643.1494373939</v>
+        <v>9948.48167251913</v>
       </c>
     </row>
     <row r="59">
@@ -1600,19 +896,7 @@
         <v>47757</v>
       </c>
       <c r="B59" t="n">
-        <v>23440.37883705537</v>
-      </c>
-      <c r="C59" t="n">
-        <v>13042.90480128124</v>
-      </c>
-      <c r="D59" t="n">
-        <v>33837.85287282951</v>
-      </c>
-      <c r="E59" t="n">
-        <v>7519.246719776229</v>
-      </c>
-      <c r="F59" t="n">
-        <v>39361.51095433451</v>
+        <v>12377.56912183404</v>
       </c>
     </row>
     <row r="60">
@@ -1620,19 +904,7 @@
         <v>47788</v>
       </c>
       <c r="B60" t="n">
-        <v>18406.36755068341</v>
-      </c>
-      <c r="C60" t="n">
-        <v>8008.893514909274</v>
-      </c>
-      <c r="D60" t="n">
-        <v>28803.84158645754</v>
-      </c>
-      <c r="E60" t="n">
-        <v>2485.235433404267</v>
-      </c>
-      <c r="F60" t="n">
-        <v>34327.49966796255</v>
+        <v>10549.91356942394</v>
       </c>
     </row>
     <row r="61">
@@ -1640,19 +912,7 @@
         <v>47818</v>
       </c>
       <c r="B61" t="n">
-        <v>19012.08499340057</v>
-      </c>
-      <c r="C61" t="n">
-        <v>8614.610957626433</v>
-      </c>
-      <c r="D61" t="n">
-        <v>29409.5590291747</v>
-      </c>
-      <c r="E61" t="n">
-        <v>3090.952876121426</v>
-      </c>
-      <c r="F61" t="n">
-        <v>34933.21711067971</v>
+        <v>11257.73761943559</v>
       </c>
     </row>
     <row r="62">
@@ -1660,19 +920,7 @@
         <v>47849</v>
       </c>
       <c r="B62" t="n">
-        <v>18626.3245085907</v>
-      </c>
-      <c r="C62" t="n">
-        <v>8228.850472816563</v>
-      </c>
-      <c r="D62" t="n">
-        <v>29023.79854436483</v>
-      </c>
-      <c r="E62" t="n">
-        <v>2705.192391311555</v>
-      </c>
-      <c r="F62" t="n">
-        <v>34547.45662586984</v>
+        <v>10689.31742399311</v>
       </c>
     </row>
     <row r="63">
@@ -1680,19 +928,7 @@
         <v>47880</v>
       </c>
       <c r="B63" t="n">
-        <v>17166.58172606276</v>
-      </c>
-      <c r="C63" t="n">
-        <v>6769.107690288625</v>
-      </c>
-      <c r="D63" t="n">
-        <v>27564.05576183689</v>
-      </c>
-      <c r="E63" t="n">
-        <v>1245.449608783618</v>
-      </c>
-      <c r="F63" t="n">
-        <v>33087.7138433419</v>
+        <v>11102.11575205329</v>
       </c>
     </row>
     <row r="64">
@@ -1700,19 +936,7 @@
         <v>47908</v>
       </c>
       <c r="B64" t="n">
-        <v>18753.93012176365</v>
-      </c>
-      <c r="C64" t="n">
-        <v>8356.456085989515</v>
-      </c>
-      <c r="D64" t="n">
-        <v>29151.40415753779</v>
-      </c>
-      <c r="E64" t="n">
-        <v>2832.798004484508</v>
-      </c>
-      <c r="F64" t="n">
-        <v>34675.06223904279</v>
+        <v>11215.52079054883</v>
       </c>
     </row>
     <row r="65">
@@ -1720,19 +944,7 @@
         <v>47939</v>
       </c>
       <c r="B65" t="n">
-        <v>19049.42812878987</v>
-      </c>
-      <c r="C65" t="n">
-        <v>8651.954093015733</v>
-      </c>
-      <c r="D65" t="n">
-        <v>29446.902164564</v>
-      </c>
-      <c r="E65" t="n">
-        <v>3128.296011510725</v>
-      </c>
-      <c r="F65" t="n">
-        <v>34970.56024606901</v>
+        <v>12772.80809771252</v>
       </c>
     </row>
     <row r="66">
@@ -1740,19 +952,7 @@
         <v>47969</v>
       </c>
       <c r="B66" t="n">
-        <v>23638.75372175295</v>
-      </c>
-      <c r="C66" t="n">
-        <v>13241.27968597881</v>
-      </c>
-      <c r="D66" t="n">
-        <v>34036.22775752708</v>
-      </c>
-      <c r="E66" t="n">
-        <v>7717.621604473805</v>
-      </c>
-      <c r="F66" t="n">
-        <v>39559.88583903209</v>
+        <v>14112.76862628989</v>
       </c>
     </row>
     <row r="67">
@@ -1760,19 +960,7 @@
         <v>48000</v>
       </c>
       <c r="B67" t="n">
-        <v>29666.41321974205</v>
-      </c>
-      <c r="C67" t="n">
-        <v>19268.93918396792</v>
-      </c>
-      <c r="D67" t="n">
-        <v>40063.88725551619</v>
-      </c>
-      <c r="E67" t="n">
-        <v>13745.28110246291</v>
-      </c>
-      <c r="F67" t="n">
-        <v>45587.5453370212</v>
+        <v>12222.19849494451</v>
       </c>
     </row>
     <row r="68">
@@ -1780,19 +968,7 @@
         <v>48030</v>
       </c>
       <c r="B68" t="n">
-        <v>21303.54560546426</v>
-      </c>
-      <c r="C68" t="n">
-        <v>10906.07156969013</v>
-      </c>
-      <c r="D68" t="n">
-        <v>31701.0196412384</v>
-      </c>
-      <c r="E68" t="n">
-        <v>5382.413488185122</v>
-      </c>
-      <c r="F68" t="n">
-        <v>37224.67772274341</v>
+        <v>11971.33897020488</v>
       </c>
     </row>
     <row r="69">
@@ -1800,19 +976,7 @@
         <v>48061</v>
       </c>
       <c r="B69" t="n">
-        <v>21270.19245109034</v>
-      </c>
-      <c r="C69" t="n">
-        <v>10872.7184153162</v>
-      </c>
-      <c r="D69" t="n">
-        <v>31667.66648686447</v>
-      </c>
-      <c r="E69" t="n">
-        <v>5349.060333811196</v>
-      </c>
-      <c r="F69" t="n">
-        <v>37191.32456836948</v>
+        <v>11554.70880520865</v>
       </c>
     </row>
     <row r="70">
@@ -1820,19 +984,7 @@
         <v>48092</v>
       </c>
       <c r="B70" t="n">
-        <v>17476.44274360484</v>
-      </c>
-      <c r="C70" t="n">
-        <v>7078.968707830705</v>
-      </c>
-      <c r="D70" t="n">
-        <v>27873.91677937897</v>
-      </c>
-      <c r="E70" t="n">
-        <v>1555.310626325698</v>
-      </c>
-      <c r="F70" t="n">
-        <v>33397.57486088398</v>
+        <v>10484.74003847223</v>
       </c>
     </row>
     <row r="71">
@@ -1840,19 +992,7 @@
         <v>48122</v>
       </c>
       <c r="B71" t="n">
-        <v>24493.9467683396</v>
-      </c>
-      <c r="C71" t="n">
-        <v>14096.47273256547</v>
-      </c>
-      <c r="D71" t="n">
-        <v>34891.42080411373</v>
-      </c>
-      <c r="E71" t="n">
-        <v>8572.814651060458</v>
-      </c>
-      <c r="F71" t="n">
-        <v>40415.07888561874</v>
+        <v>12913.82930911427</v>
       </c>
     </row>
     <row r="72">
@@ -1860,19 +1000,7 @@
         <v>48153</v>
       </c>
       <c r="B72" t="n">
-        <v>19230.58607264247</v>
-      </c>
-      <c r="C72" t="n">
-        <v>8833.112036868339</v>
-      </c>
-      <c r="D72" t="n">
-        <v>29628.0601084166</v>
-      </c>
-      <c r="E72" t="n">
-        <v>3309.453955363331</v>
-      </c>
-      <c r="F72" t="n">
-        <v>35151.71818992162</v>
+        <v>11086.17268661362</v>
       </c>
     </row>
     <row r="73">
@@ -1880,19 +1008,7 @@
         <v>48183</v>
       </c>
       <c r="B73" t="n">
-        <v>19860.26188784253</v>
-      </c>
-      <c r="C73" t="n">
-        <v>9462.787852068397</v>
-      </c>
-      <c r="D73" t="n">
-        <v>30257.73592361667</v>
-      </c>
-      <c r="E73" t="n">
-        <v>3939.12977056339</v>
-      </c>
-      <c r="F73" t="n">
-        <v>35781.39400512167</v>
+        <v>11793.99732720092</v>
       </c>
     </row>
     <row r="74">
@@ -1900,19 +1016,7 @@
         <v>48214</v>
       </c>
       <c r="B74" t="n">
-        <v>19454.21380641875</v>
-      </c>
-      <c r="C74" t="n">
-        <v>9056.739770644615</v>
-      </c>
-      <c r="D74" t="n">
-        <v>29851.68784219289</v>
-      </c>
-      <c r="E74" t="n">
-        <v>3533.081689139608</v>
-      </c>
-      <c r="F74" t="n">
-        <v>35375.34592369789</v>
+        <v>11225.57680500513</v>
       </c>
     </row>
     <row r="75">
@@ -1920,19 +1024,7 @@
         <v>48245</v>
       </c>
       <c r="B75" t="n">
-        <v>17926.7737354433</v>
-      </c>
-      <c r="C75" t="n">
-        <v>7529.299699669171</v>
-      </c>
-      <c r="D75" t="n">
-        <v>28324.24777121744</v>
-      </c>
-      <c r="E75" t="n">
-        <v>2005.641618164163</v>
-      </c>
-      <c r="F75" t="n">
-        <v>33847.90585272245</v>
+        <v>11638.37521364407</v>
       </c>
     </row>
     <row r="76">
@@ -1940,19 +1032,7 @@
         <v>48274</v>
       </c>
       <c r="B76" t="n">
-        <v>19581.36162878784</v>
-      </c>
-      <c r="C76" t="n">
-        <v>9183.887593013702</v>
-      </c>
-      <c r="D76" t="n">
-        <v>29978.83566456197</v>
-      </c>
-      <c r="E76" t="n">
-        <v>3660.229511508694</v>
-      </c>
-      <c r="F76" t="n">
-        <v>35502.49374606698</v>
+        <v>11751.7802199022</v>
       </c>
     </row>
     <row r="77">
@@ -1960,19 +1040,7 @@
         <v>48305</v>
       </c>
       <c r="B77" t="n">
-        <v>19886.81830096068</v>
-      </c>
-      <c r="C77" t="n">
-        <v>9489.344265186543</v>
-      </c>
-      <c r="D77" t="n">
-        <v>30284.29233673481</v>
-      </c>
-      <c r="E77" t="n">
-        <v>3965.686183681535</v>
-      </c>
-      <c r="F77" t="n">
-        <v>35807.95041823982</v>
+        <v>13309.06761021244</v>
       </c>
     </row>
     <row r="78">
@@ -1980,19 +1048,7 @@
         <v>48335</v>
       </c>
       <c r="B78" t="n">
-        <v>24674.09249271142</v>
-      </c>
-      <c r="C78" t="n">
-        <v>14276.61845693728</v>
-      </c>
-      <c r="D78" t="n">
-        <v>35071.56652848555</v>
-      </c>
-      <c r="E78" t="n">
-        <v>8752.960375432276</v>
-      </c>
-      <c r="F78" t="n">
-        <v>40595.22460999056</v>
+        <v>14649.02817644912</v>
       </c>
     </row>
     <row r="79">
@@ -2000,19 +1056,7 @@
         <v>48366</v>
       </c>
       <c r="B79" t="n">
-        <v>30961.0284541052</v>
-      </c>
-      <c r="C79" t="n">
-        <v>20563.55441833106</v>
-      </c>
-      <c r="D79" t="n">
-        <v>41358.50248987933</v>
-      </c>
-      <c r="E79" t="n">
-        <v>15039.89633682605</v>
-      </c>
-      <c r="F79" t="n">
-        <v>46882.16057138434</v>
+        <v>12758.45794881714</v>
       </c>
     </row>
     <row r="80">
@@ -2020,19 +1064,7 @@
         <v>48396</v>
       </c>
       <c r="B80" t="n">
-        <v>22229.84434980759</v>
-      </c>
-      <c r="C80" t="n">
-        <v>11832.37031403346</v>
-      </c>
-      <c r="D80" t="n">
-        <v>32627.31838558173</v>
-      </c>
-      <c r="E80" t="n">
-        <v>6308.712232528453</v>
-      </c>
-      <c r="F80" t="n">
-        <v>38150.97646708674</v>
+        <v>12507.59835348272</v>
       </c>
     </row>
     <row r="81">
@@ -2040,19 +1072,7 @@
         <v>48427</v>
       </c>
       <c r="B81" t="n">
-        <v>22191.701957757</v>
-      </c>
-      <c r="C81" t="n">
-        <v>11794.22792198287</v>
-      </c>
-      <c r="D81" t="n">
-        <v>32589.17599353113</v>
-      </c>
-      <c r="E81" t="n">
-        <v>6270.569840477861</v>
-      </c>
-      <c r="F81" t="n">
-        <v>38112.83407503615</v>
+        <v>12090.96817502179</v>
       </c>
     </row>
     <row r="82">
@@ -2060,19 +1080,7 @@
         <v>48458</v>
       </c>
       <c r="B82" t="n">
-        <v>18230.86816709492</v>
-      </c>
-      <c r="C82" t="n">
-        <v>7833.394131320785</v>
-      </c>
-      <c r="D82" t="n">
-        <v>28628.34220286905</v>
-      </c>
-      <c r="E82" t="n">
-        <v>2309.736049815778</v>
-      </c>
-      <c r="F82" t="n">
-        <v>34152.00028437406</v>
+        <v>11020.99941602247</v>
       </c>
     </row>
     <row r="83">
@@ -2080,19 +1088,7 @@
         <v>48488</v>
       </c>
       <c r="B83" t="n">
-        <v>25547.51469962382</v>
-      </c>
-      <c r="C83" t="n">
-        <v>15150.04066384969</v>
-      </c>
-      <c r="D83" t="n">
-        <v>35944.98873539796</v>
-      </c>
-      <c r="E83" t="n">
-        <v>9626.38258234468</v>
-      </c>
-      <c r="F83" t="n">
-        <v>41468.64681690296</v>
+        <v>13450.08879383746</v>
       </c>
     </row>
     <row r="84">
@@ -2100,19 +1096,7 @@
         <v>48519</v>
       </c>
       <c r="B84" t="n">
-        <v>20054.80459460154</v>
-      </c>
-      <c r="C84" t="n">
-        <v>9657.330558827407</v>
-      </c>
-      <c r="D84" t="n">
-        <v>30452.27863037567</v>
-      </c>
-      <c r="E84" t="n">
-        <v>4133.6724773224</v>
-      </c>
-      <c r="F84" t="n">
-        <v>35975.93671188068</v>
+        <v>11622.43210836912</v>
       </c>
     </row>
     <row r="85">
@@ -2120,19 +1104,7 @@
         <v>48549</v>
       </c>
       <c r="B85" t="n">
-        <v>20708.4387822845</v>
-      </c>
-      <c r="C85" t="n">
-        <v>10310.96474651036</v>
-      </c>
-      <c r="D85" t="n">
-        <v>31105.91281805863</v>
-      </c>
-      <c r="E85" t="n">
-        <v>4787.306665005357</v>
-      </c>
-      <c r="F85" t="n">
-        <v>36629.57089956364</v>
+        <v>12330.25678370786</v>
       </c>
     </row>
     <row r="86">
@@ -2140,19 +1112,7 @@
         <v>48580</v>
       </c>
       <c r="B86" t="n">
-        <v>20282.1031042468</v>
-      </c>
-      <c r="C86" t="n">
-        <v>9884.629068472665</v>
-      </c>
-      <c r="D86" t="n">
-        <v>30679.57714002093</v>
-      </c>
-      <c r="E86" t="n">
-        <v>4360.970986967657</v>
-      </c>
-      <c r="F86" t="n">
-        <v>36203.23522152594</v>
+        <v>11761.83624228482</v>
       </c>
     </row>
     <row r="87">
@@ -2160,19 +1120,7 @@
         <v>48611</v>
       </c>
       <c r="B87" t="n">
-        <v>18686.96574482384</v>
-      </c>
-      <c r="C87" t="n">
-        <v>8289.491709049709</v>
-      </c>
-      <c r="D87" t="n">
-        <v>29084.43978059798</v>
-      </c>
-      <c r="E87" t="n">
-        <v>2765.833627544702</v>
-      </c>
-      <c r="F87" t="n">
-        <v>34608.09786210299</v>
+        <v>12174.63465566528</v>
       </c>
     </row>
     <row r="88">
@@ -2180,19 +1128,7 @@
         <v>48639</v>
       </c>
       <c r="B88" t="n">
-        <v>20408.79313581202</v>
-      </c>
-      <c r="C88" t="n">
-        <v>10011.31910003789</v>
-      </c>
-      <c r="D88" t="n">
-        <v>30806.26717158616</v>
-      </c>
-      <c r="E88" t="n">
-        <v>4487.661018532881</v>
-      </c>
-      <c r="F88" t="n">
-        <v>36329.92525309116</v>
+        <v>12288.03966002645</v>
       </c>
     </row>
     <row r="89">
@@ -2200,19 +1136,7 @@
         <v>48670</v>
       </c>
       <c r="B89" t="n">
-        <v>20724.20847313148</v>
-      </c>
-      <c r="C89" t="n">
-        <v>10326.73443735735</v>
-      </c>
-      <c r="D89" t="n">
-        <v>31121.68250890561</v>
-      </c>
-      <c r="E89" t="n">
-        <v>4803.076355852341</v>
-      </c>
-      <c r="F89" t="n">
-        <v>36645.34059041063</v>
+        <v>13845.32705522931</v>
       </c>
     </row>
     <row r="90">
@@ -2220,19 +1144,7 @@
         <v>48700</v>
       </c>
       <c r="B90" t="n">
-        <v>25709.43126366989</v>
-      </c>
-      <c r="C90" t="n">
-        <v>15311.95722789575</v>
-      </c>
-      <c r="D90" t="n">
-        <v>36106.90529944402</v>
-      </c>
-      <c r="E90" t="n">
-        <v>9788.299146390747</v>
-      </c>
-      <c r="F90" t="n">
-        <v>41630.56338094903</v>
+        <v>15185.287623682</v>
       </c>
     </row>
     <row r="91">
@@ -2240,19 +1152,7 @@
         <v>48731</v>
       </c>
       <c r="B91" t="n">
-        <v>32255.64368846834</v>
-      </c>
-      <c r="C91" t="n">
-        <v>21858.1696526942</v>
-      </c>
-      <c r="D91" t="n">
-        <v>42653.11772424247</v>
-      </c>
-      <c r="E91" t="n">
-        <v>16334.51157118919</v>
-      </c>
-      <c r="F91" t="n">
-        <v>48176.77580574748</v>
+        <v>13294.71739038419</v>
       </c>
     </row>
     <row r="92">
@@ -2260,19 +1160,7 @@
         <v>48761</v>
       </c>
       <c r="B92" t="n">
-        <v>23156.14309415092</v>
-      </c>
-      <c r="C92" t="n">
-        <v>12758.66905837679</v>
-      </c>
-      <c r="D92" t="n">
-        <v>33553.61712992506</v>
-      </c>
-      <c r="E92" t="n">
-        <v>7235.010976871783</v>
-      </c>
-      <c r="F92" t="n">
-        <v>39077.27521143007</v>
+        <v>13043.85779089573</v>
       </c>
     </row>
     <row r="93">
@@ -2280,19 +1168,7 @@
         <v>48792</v>
       </c>
       <c r="B93" t="n">
-        <v>23113.21146442366</v>
-      </c>
-      <c r="C93" t="n">
-        <v>12715.73742864953</v>
-      </c>
-      <c r="D93" t="n">
-        <v>33510.6855001978</v>
-      </c>
-      <c r="E93" t="n">
-        <v>7192.079347144523</v>
-      </c>
-      <c r="F93" t="n">
-        <v>39034.34358170281</v>
+        <v>12627.2276116425</v>
       </c>
     </row>
     <row r="94">
@@ -2300,19 +1176,7 @@
         <v>48823</v>
       </c>
       <c r="B94" t="n">
-        <v>18985.293590585</v>
-      </c>
-      <c r="C94" t="n">
-        <v>8587.819554810869</v>
-      </c>
-      <c r="D94" t="n">
-        <v>29382.76762635913</v>
-      </c>
-      <c r="E94" t="n">
-        <v>3064.161473305861</v>
-      </c>
-      <c r="F94" t="n">
-        <v>34906.42570786415</v>
+        <v>11557.25885309845</v>
       </c>
     </row>
     <row r="95">
@@ -2320,19 +1184,7 @@
         <v>48853</v>
       </c>
       <c r="B95" t="n">
-        <v>26601.08263090805</v>
-      </c>
-      <c r="C95" t="n">
-        <v>16203.60859513391</v>
-      </c>
-      <c r="D95" t="n">
-        <v>36998.55666668218</v>
-      </c>
-      <c r="E95" t="n">
-        <v>10679.95051362891</v>
-      </c>
-      <c r="F95" t="n">
-        <v>42522.21474818719</v>
+        <v>13986.34823721986</v>
       </c>
     </row>
     <row r="96">
@@ -2340,19 +1192,7 @@
         <v>48884</v>
       </c>
       <c r="B96" t="n">
-        <v>20879.02311656061</v>
-      </c>
-      <c r="C96" t="n">
-        <v>10481.54908078647</v>
-      </c>
-      <c r="D96" t="n">
-        <v>31276.49715233474</v>
-      </c>
-      <c r="E96" t="n">
-        <v>4957.890999281464</v>
-      </c>
-      <c r="F96" t="n">
-        <v>36800.15523383975</v>
+        <v>12158.69154804629</v>
       </c>
     </row>
     <row r="97">
@@ -2360,19 +1200,7 @@
         <v>48914</v>
       </c>
       <c r="B97" t="n">
-        <v>21556.61567672647</v>
-      </c>
-      <c r="C97" t="n">
-        <v>11159.14164095233</v>
-      </c>
-      <c r="D97" t="n">
-        <v>31954.0897125006</v>
-      </c>
-      <c r="E97" t="n">
-        <v>5635.483559447324</v>
-      </c>
-      <c r="F97" t="n">
-        <v>37477.74779400561</v>
+        <v>12866.51622542992</v>
       </c>
     </row>
     <row r="98">
@@ -2380,19 +1208,7 @@
         <v>48945</v>
       </c>
       <c r="B98" t="n">
-        <v>21109.99240207485</v>
-      </c>
-      <c r="C98" t="n">
-        <v>10712.51836630072</v>
-      </c>
-      <c r="D98" t="n">
-        <v>31507.46643784899</v>
-      </c>
-      <c r="E98" t="n">
-        <v>5188.860284795714</v>
-      </c>
-      <c r="F98" t="n">
-        <v>37031.12451935399</v>
+        <v>12298.09568287548</v>
       </c>
     </row>
     <row r="99">
@@ -2400,19 +1216,7 @@
         <v>48976</v>
       </c>
       <c r="B99" t="n">
-        <v>19447.15775420439</v>
-      </c>
-      <c r="C99" t="n">
-        <v>9049.683718430251</v>
-      </c>
-      <c r="D99" t="n">
-        <v>29844.63178997852</v>
-      </c>
-      <c r="E99" t="n">
-        <v>3526.025636925244</v>
-      </c>
-      <c r="F99" t="n">
-        <v>35368.28987148352</v>
+        <v>12710.89409653495</v>
       </c>
     </row>
     <row r="100">
@@ -2420,19 +1224,7 @@
         <v>49004</v>
       </c>
       <c r="B100" t="n">
-        <v>21236.22464283621</v>
-      </c>
-      <c r="C100" t="n">
-        <v>10838.75060706207</v>
-      </c>
-      <c r="D100" t="n">
-        <v>31633.69867861034</v>
-      </c>
-      <c r="E100" t="n">
-        <v>5315.092525557067</v>
-      </c>
-      <c r="F100" t="n">
-        <v>37157.35676011535</v>
+        <v>12824.2991007845</v>
       </c>
     </row>
     <row r="101">
@@ -2440,19 +1232,7 @@
         <v>49035</v>
       </c>
       <c r="B101" t="n">
-        <v>21561.59864530229</v>
-      </c>
-      <c r="C101" t="n">
-        <v>11164.12460952816</v>
-      </c>
-      <c r="D101" t="n">
-        <v>31959.07268107642</v>
-      </c>
-      <c r="E101" t="n">
-        <v>5640.466528023151</v>
-      </c>
-      <c r="F101" t="n">
-        <v>37482.73076258144</v>
+        <v>14381.58649627525</v>
       </c>
     </row>
     <row r="102">
@@ -2460,19 +1240,7 @@
         <v>49065</v>
       </c>
       <c r="B102" t="n">
-        <v>26744.77003462836</v>
-      </c>
-      <c r="C102" t="n">
-        <v>16347.29599885423</v>
-      </c>
-      <c r="D102" t="n">
-        <v>37142.2440704025</v>
-      </c>
-      <c r="E102" t="n">
-        <v>10823.63791734922</v>
-      </c>
-      <c r="F102" t="n">
-        <v>42665.9021519075</v>
+        <v>15721.54706485833</v>
       </c>
     </row>
     <row r="103">
@@ -2480,19 +1248,7 @@
         <v>49096</v>
       </c>
       <c r="B103" t="n">
-        <v>33550.25892283148</v>
-      </c>
-      <c r="C103" t="n">
-        <v>23152.78488705734</v>
-      </c>
-      <c r="D103" t="n">
-        <v>43947.73295860561</v>
-      </c>
-      <c r="E103" t="n">
-        <v>17629.12680555233</v>
-      </c>
-      <c r="F103" t="n">
-        <v>49471.39104011062</v>
+        <v>13830.97683122713</v>
       </c>
     </row>
     <row r="104">
@@ -2500,19 +1256,7 @@
         <v>49126</v>
       </c>
       <c r="B104" t="n">
-        <v>24082.44183849425</v>
-      </c>
-      <c r="C104" t="n">
-        <v>13684.96780272012</v>
-      </c>
-      <c r="D104" t="n">
-        <v>34479.91587426839</v>
-      </c>
-      <c r="E104" t="n">
-        <v>8161.30972121511</v>
-      </c>
-      <c r="F104" t="n">
-        <v>40003.57395577339</v>
+        <v>13580.11723149424</v>
       </c>
     </row>
     <row r="105">
@@ -2520,19 +1264,7 @@
         <v>49157</v>
       </c>
       <c r="B105" t="n">
-        <v>24034.72097109033</v>
-      </c>
-      <c r="C105" t="n">
-        <v>13637.2469353162</v>
-      </c>
-      <c r="D105" t="n">
-        <v>34432.19500686447</v>
-      </c>
-      <c r="E105" t="n">
-        <v>8113.588853811189</v>
-      </c>
-      <c r="F105" t="n">
-        <v>39955.85308836947</v>
+        <v>13163.48705219438</v>
       </c>
     </row>
     <row r="106">
@@ -2540,19 +1272,7 @@
         <v>49188</v>
       </c>
       <c r="B106" t="n">
-        <v>19739.71901407509</v>
-      </c>
-      <c r="C106" t="n">
-        <v>9342.244978300956</v>
-      </c>
-      <c r="D106" t="n">
-        <v>30137.19304984922</v>
-      </c>
-      <c r="E106" t="n">
-        <v>3818.586896795949</v>
-      </c>
-      <c r="F106" t="n">
-        <v>35660.85113135423</v>
+        <v>12093.51829367713</v>
       </c>
     </row>
     <row r="107">
@@ -2560,19 +1280,7 @@
         <v>49218</v>
       </c>
       <c r="B107" t="n">
-        <v>27654.65056219227</v>
-      </c>
-      <c r="C107" t="n">
-        <v>17257.17652641814</v>
-      </c>
-      <c r="D107" t="n">
-        <v>38052.1245979664</v>
-      </c>
-      <c r="E107" t="n">
-        <v>11733.51844491313</v>
-      </c>
-      <c r="F107" t="n">
-        <v>43575.78267947141</v>
+        <v>14522.60767816962</v>
       </c>
     </row>
     <row r="108">
@@ -2580,19 +1288,7 @@
         <v>49249</v>
       </c>
       <c r="B108" t="n">
-        <v>21703.24163851967</v>
-      </c>
-      <c r="C108" t="n">
-        <v>11305.76760274554</v>
-      </c>
-      <c r="D108" t="n">
-        <v>32100.71567429381</v>
-      </c>
-      <c r="E108" t="n">
-        <v>5782.109521240533</v>
-      </c>
-      <c r="F108" t="n">
-        <v>37624.37375579881</v>
+        <v>12694.95098877803</v>
       </c>
     </row>
     <row r="109">
@@ -2600,19 +1296,7 @@
         <v>49279</v>
       </c>
       <c r="B109" t="n">
-        <v>22404.79257116843</v>
-      </c>
-      <c r="C109" t="n">
-        <v>12007.3185353943</v>
-      </c>
-      <c r="D109" t="n">
-        <v>32802.26660694256</v>
-      </c>
-      <c r="E109" t="n">
-        <v>6483.660453889288</v>
-      </c>
-      <c r="F109" t="n">
-        <v>38325.92468844757</v>
+        <v>13402.77566628198</v>
       </c>
     </row>
     <row r="110">
@@ -2620,19 +1304,7 @@
         <v>49310</v>
       </c>
       <c r="B110" t="n">
-        <v>21937.8816999029</v>
-      </c>
-      <c r="C110" t="n">
-        <v>11540.40766412877</v>
-      </c>
-      <c r="D110" t="n">
-        <v>32335.35573567704</v>
-      </c>
-      <c r="E110" t="n">
-        <v>6016.749582623763</v>
-      </c>
-      <c r="F110" t="n">
-        <v>37859.01381718204</v>
+        <v>12834.35512366097</v>
       </c>
     </row>
     <row r="111">
@@ -2640,19 +1312,7 @@
         <v>49341</v>
       </c>
       <c r="B111" t="n">
-        <v>20207.34976358492</v>
-      </c>
-      <c r="C111" t="n">
-        <v>9809.87572781079</v>
-      </c>
-      <c r="D111" t="n">
-        <v>30604.82379935906</v>
-      </c>
-      <c r="E111" t="n">
-        <v>4286.217646305782</v>
-      </c>
-      <c r="F111" t="n">
-        <v>36128.48188086406</v>
+        <v>13247.15353733686</v>
       </c>
     </row>
     <row r="112">
@@ -2660,19 +1320,7 @@
         <v>49369</v>
       </c>
       <c r="B112" t="n">
-        <v>22063.6561498604</v>
-      </c>
-      <c r="C112" t="n">
-        <v>11666.18211408626</v>
-      </c>
-      <c r="D112" t="n">
-        <v>32461.13018563453</v>
-      </c>
-      <c r="E112" t="n">
-        <v>6142.524032581254</v>
-      </c>
-      <c r="F112" t="n">
-        <v>37984.78826713953</v>
+        <v>13360.55854157984</v>
       </c>
     </row>
     <row r="113">
@@ -2680,19 +1328,7 @@
         <v>49400</v>
       </c>
       <c r="B113" t="n">
-        <v>22398.9888174731</v>
-      </c>
-      <c r="C113" t="n">
-        <v>12001.51478169896</v>
-      </c>
-      <c r="D113" t="n">
-        <v>32796.46285324723</v>
-      </c>
-      <c r="E113" t="n">
-        <v>6477.856700193957</v>
-      </c>
-      <c r="F113" t="n">
-        <v>38320.12093475224</v>
+        <v>14917.84593708753</v>
       </c>
     </row>
     <row r="114">
@@ -2700,19 +1336,7 @@
         <v>49430</v>
       </c>
       <c r="B114" t="n">
-        <v>27780.10880558683</v>
-      </c>
-      <c r="C114" t="n">
-        <v>17382.6347698127</v>
-      </c>
-      <c r="D114" t="n">
-        <v>38177.58284136097</v>
-      </c>
-      <c r="E114" t="n">
-        <v>11858.97668830769</v>
-      </c>
-      <c r="F114" t="n">
-        <v>43701.24092286597</v>
+        <v>16257.80650567829</v>
       </c>
     </row>
     <row r="115">
@@ -2720,19 +1344,7 @@
         <v>49461</v>
       </c>
       <c r="B115" t="n">
-        <v>34844.87415719462</v>
-      </c>
-      <c r="C115" t="n">
-        <v>24447.40012142048</v>
-      </c>
-      <c r="D115" t="n">
-        <v>45242.34819296875</v>
-      </c>
-      <c r="E115" t="n">
-        <v>18923.74203991547</v>
-      </c>
-      <c r="F115" t="n">
-        <v>50766.00627447376</v>
+        <v>14367.23627202747</v>
       </c>
     </row>
     <row r="116">
@@ -2740,19 +1352,7 @@
         <v>49491</v>
       </c>
       <c r="B116" t="n">
-        <v>25008.74058283758</v>
-      </c>
-      <c r="C116" t="n">
-        <v>14611.26654706345</v>
-      </c>
-      <c r="D116" t="n">
-        <v>35406.21461861172</v>
-      </c>
-      <c r="E116" t="n">
-        <v>9087.60846555844</v>
-      </c>
-      <c r="F116" t="n">
-        <v>40929.87270011672</v>
+        <v>14116.37667228019</v>
       </c>
     </row>
     <row r="117">
@@ -2760,19 +1360,7 @@
         <v>49522</v>
       </c>
       <c r="B117" t="n">
-        <v>24956.23047775699</v>
-      </c>
-      <c r="C117" t="n">
-        <v>14558.75644198286</v>
-      </c>
-      <c r="D117" t="n">
-        <v>35353.70451353113</v>
-      </c>
-      <c r="E117" t="n">
-        <v>9035.09836047785</v>
-      </c>
-      <c r="F117" t="n">
-        <v>40877.36259503613</v>
+        <v>13699.74649297759</v>
       </c>
     </row>
     <row r="118">
@@ -2780,19 +1368,7 @@
         <v>49553</v>
       </c>
       <c r="B118" t="n">
-        <v>20494.14443756517</v>
-      </c>
-      <c r="C118" t="n">
-        <v>10096.67040179104</v>
-      </c>
-      <c r="D118" t="n">
-        <v>30891.61847333931</v>
-      </c>
-      <c r="E118" t="n">
-        <v>4573.012320286032</v>
-      </c>
-      <c r="F118" t="n">
-        <v>36415.27655484431</v>
+        <v>12629.77773446191</v>
       </c>
     </row>
     <row r="119">
@@ -2800,19 +1376,7 @@
         <v>49583</v>
       </c>
       <c r="B119" t="n">
-        <v>28708.21849347649</v>
-      </c>
-      <c r="C119" t="n">
-        <v>18310.74445770236</v>
-      </c>
-      <c r="D119" t="n">
-        <v>39105.69252925063</v>
-      </c>
-      <c r="E119" t="n">
-        <v>12787.08637619735</v>
-      </c>
-      <c r="F119" t="n">
-        <v>44629.35061075563</v>
+        <v>15058.86711897624</v>
       </c>
     </row>
     <row r="120">
@@ -2820,19 +1384,7 @@
         <v>49614</v>
       </c>
       <c r="B120" t="n">
-        <v>22527.46016047874</v>
-      </c>
-      <c r="C120" t="n">
-        <v>12129.9861247046</v>
-      </c>
-      <c r="D120" t="n">
-        <v>32924.93419625287</v>
-      </c>
-      <c r="E120" t="n">
-        <v>6606.328043199597</v>
-      </c>
-      <c r="F120" t="n">
-        <v>38448.59227775788</v>
+        <v>13231.21042957182</v>
       </c>
     </row>
     <row r="121">
@@ -2840,19 +1392,7 @@
         <v>49644</v>
       </c>
       <c r="B121" t="n">
-        <v>23252.9694656104</v>
-      </c>
-      <c r="C121" t="n">
-        <v>12855.49542983626</v>
-      </c>
-      <c r="D121" t="n">
-        <v>33650.44350138453</v>
-      </c>
-      <c r="E121" t="n">
-        <v>7331.837348331255</v>
-      </c>
-      <c r="F121" t="n">
-        <v>39174.10158288954</v>
+        <v>13939.03510708285</v>
       </c>
     </row>
   </sheetData>
@@ -2866,7 +1406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F121"/>
+  <dimension ref="A1:B121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2880,45 +1420,13 @@
           <t>forecast</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ci80_lower</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>ci80_upper</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>ci95_lower</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>ci95_upper</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>161.7585257218375</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-2056.123439097868</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2379.640490541543</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-3234.373232908337</v>
-      </c>
-      <c r="F2" t="n">
-        <v>3557.890284352012</v>
+        <v>8279.46279176329</v>
       </c>
     </row>
     <row r="3">
@@ -2926,19 +1434,7 @@
         <v>46054</v>
       </c>
       <c r="B3" t="n">
-        <v>4267.342541321517</v>
-      </c>
-      <c r="C3" t="n">
-        <v>2049.460576501811</v>
-      </c>
-      <c r="D3" t="n">
-        <v>6485.224506141223</v>
-      </c>
-      <c r="E3" t="n">
-        <v>871.210782691343</v>
-      </c>
-      <c r="F3" t="n">
-        <v>7663.474299951691</v>
+        <v>8513.768015517546</v>
       </c>
     </row>
     <row r="4">
@@ -2946,19 +1442,7 @@
         <v>46082</v>
       </c>
       <c r="B4" t="n">
-        <v>8200.622499654346</v>
-      </c>
-      <c r="C4" t="n">
-        <v>5982.74053483464</v>
-      </c>
-      <c r="D4" t="n">
-        <v>10418.50446447405</v>
-      </c>
-      <c r="E4" t="n">
-        <v>4804.490741024172</v>
-      </c>
-      <c r="F4" t="n">
-        <v>11596.75425828452</v>
+        <v>8194.928461414989</v>
       </c>
     </row>
     <row r="5">
@@ -2966,19 +1450,7 @@
         <v>46113</v>
       </c>
       <c r="B5" t="n">
-        <v>7748.424472191156</v>
-      </c>
-      <c r="C5" t="n">
-        <v>5530.54250737145</v>
-      </c>
-      <c r="D5" t="n">
-        <v>9966.306437010862</v>
-      </c>
-      <c r="E5" t="n">
-        <v>4352.292713560983</v>
-      </c>
-      <c r="F5" t="n">
-        <v>11144.55623082133</v>
+        <v>8230.784120420736</v>
       </c>
     </row>
     <row r="6">
@@ -2986,19 +1458,7 @@
         <v>46143</v>
       </c>
       <c r="B6" t="n">
-        <v>8105.604718491236</v>
-      </c>
-      <c r="C6" t="n">
-        <v>5887.72275367153</v>
-      </c>
-      <c r="D6" t="n">
-        <v>10323.48668331094</v>
-      </c>
-      <c r="E6" t="n">
-        <v>4709.472959861061</v>
-      </c>
-      <c r="F6" t="n">
-        <v>11501.73647712141</v>
+        <v>8049.697388520468</v>
       </c>
     </row>
     <row r="7">
@@ -3006,19 +1466,7 @@
         <v>46174</v>
       </c>
       <c r="B7" t="n">
-        <v>8587.238232071159</v>
-      </c>
-      <c r="C7" t="n">
-        <v>6369.356267251453</v>
-      </c>
-      <c r="D7" t="n">
-        <v>10805.12019689086</v>
-      </c>
-      <c r="E7" t="n">
-        <v>5191.106473440985</v>
-      </c>
-      <c r="F7" t="n">
-        <v>11983.36999070133</v>
+        <v>8217.261216639274</v>
       </c>
     </row>
     <row r="8">
@@ -3026,19 +1474,7 @@
         <v>46204</v>
       </c>
       <c r="B8" t="n">
-        <v>9686.551951244779</v>
-      </c>
-      <c r="C8" t="n">
-        <v>7468.669986425073</v>
-      </c>
-      <c r="D8" t="n">
-        <v>11904.43391606448</v>
-      </c>
-      <c r="E8" t="n">
-        <v>6290.420192614605</v>
-      </c>
-      <c r="F8" t="n">
-        <v>13082.68370987495</v>
+        <v>8650.665917364169</v>
       </c>
     </row>
     <row r="9">
@@ -3046,19 +1482,7 @@
         <v>46235</v>
       </c>
       <c r="B9" t="n">
-        <v>9839.46321282739</v>
-      </c>
-      <c r="C9" t="n">
-        <v>7621.581248007684</v>
-      </c>
-      <c r="D9" t="n">
-        <v>12057.3451776471</v>
-      </c>
-      <c r="E9" t="n">
-        <v>6443.331454197216</v>
-      </c>
-      <c r="F9" t="n">
-        <v>13235.59497145756</v>
+        <v>8789.20595131068</v>
       </c>
     </row>
     <row r="10">
@@ -3066,19 +1490,7 @@
         <v>46266</v>
       </c>
       <c r="B10" t="n">
-        <v>8693.461865949312</v>
-      </c>
-      <c r="C10" t="n">
-        <v>6475.579901129606</v>
-      </c>
-      <c r="D10" t="n">
-        <v>10911.34383076902</v>
-      </c>
-      <c r="E10" t="n">
-        <v>5297.330107319138</v>
-      </c>
-      <c r="F10" t="n">
-        <v>12089.59362457949</v>
+        <v>8779.584222108348</v>
       </c>
     </row>
     <row r="11">
@@ -3086,19 +1498,7 @@
         <v>46296</v>
       </c>
       <c r="B11" t="n">
-        <v>8402.821358006106</v>
-      </c>
-      <c r="C11" t="n">
-        <v>6184.9393931864</v>
-      </c>
-      <c r="D11" t="n">
-        <v>10620.70332282581</v>
-      </c>
-      <c r="E11" t="n">
-        <v>5006.689599375932</v>
-      </c>
-      <c r="F11" t="n">
-        <v>11798.95311663628</v>
+        <v>8831.429101859925</v>
       </c>
     </row>
     <row r="12">
@@ -3106,19 +1506,7 @@
         <v>46327</v>
       </c>
       <c r="B12" t="n">
-        <v>8641.316458839294</v>
-      </c>
-      <c r="C12" t="n">
-        <v>6423.434494019588</v>
-      </c>
-      <c r="D12" t="n">
-        <v>10859.198423659</v>
-      </c>
-      <c r="E12" t="n">
-        <v>5245.18470020912</v>
-      </c>
-      <c r="F12" t="n">
-        <v>12037.44821746947</v>
+        <v>8621.173989634804</v>
       </c>
     </row>
     <row r="13">
@@ -3126,19 +1514,7 @@
         <v>46357</v>
       </c>
       <c r="B13" t="n">
-        <v>9577.810271204948</v>
-      </c>
-      <c r="C13" t="n">
-        <v>7359.928306385242</v>
-      </c>
-      <c r="D13" t="n">
-        <v>11795.69223602465</v>
-      </c>
-      <c r="E13" t="n">
-        <v>6181.678512574774</v>
-      </c>
-      <c r="F13" t="n">
-        <v>12973.94202983512</v>
+        <v>8722.908123150368</v>
       </c>
     </row>
     <row r="14">
@@ -3146,19 +1522,7 @@
         <v>46388</v>
       </c>
       <c r="B14" t="n">
-        <v>169.3856117060969</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-2048.496353113609</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2387.267576525803</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-3226.746146924077</v>
-      </c>
-      <c r="F14" t="n">
-        <v>3565.517370336271</v>
+        <v>8592.523412594412</v>
       </c>
     </row>
     <row r="15">
@@ -3166,19 +1530,7 @@
         <v>46419</v>
       </c>
       <c r="B15" t="n">
-        <v>4467.764756389636</v>
-      </c>
-      <c r="C15" t="n">
-        <v>2249.88279156993</v>
-      </c>
-      <c r="D15" t="n">
-        <v>6685.646721209342</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1071.632997759462</v>
-      </c>
-      <c r="F15" t="n">
-        <v>7863.896515019811</v>
+        <v>8936.421798245427</v>
       </c>
     </row>
     <row r="16">
@@ -3186,19 +1538,7 @@
         <v>46447</v>
       </c>
       <c r="B16" t="n">
-        <v>8584.275603054946</v>
-      </c>
-      <c r="C16" t="n">
-        <v>6366.39363823524</v>
-      </c>
-      <c r="D16" t="n">
-        <v>10802.15756787465</v>
-      </c>
-      <c r="E16" t="n">
-        <v>5188.143844424772</v>
-      </c>
-      <c r="F16" t="n">
-        <v>11980.40736168512</v>
+        <v>8581.994037781835</v>
       </c>
     </row>
     <row r="17">
@@ -3206,19 +1546,7 @@
         <v>46478</v>
       </c>
       <c r="B17" t="n">
-        <v>8109.514457035403</v>
-      </c>
-      <c r="C17" t="n">
-        <v>5891.632492215697</v>
-      </c>
-      <c r="D17" t="n">
-        <v>10327.39642185511</v>
-      </c>
-      <c r="E17" t="n">
-        <v>4713.382698405228</v>
-      </c>
-      <c r="F17" t="n">
-        <v>11505.64621566558</v>
+        <v>8538.947850928353</v>
       </c>
     </row>
     <row r="18">
@@ -3226,19 +1554,7 @@
         <v>46508</v>
       </c>
       <c r="B18" t="n">
-        <v>8481.878669299043</v>
-      </c>
-      <c r="C18" t="n">
-        <v>6263.996704479337</v>
-      </c>
-      <c r="D18" t="n">
-        <v>10699.76063411875</v>
-      </c>
-      <c r="E18" t="n">
-        <v>5085.74691066887</v>
-      </c>
-      <c r="F18" t="n">
-        <v>11878.01042792922</v>
+        <v>8409.021404123645</v>
       </c>
     </row>
     <row r="19">
@@ -3246,19 +1562,7 @@
         <v>46539</v>
       </c>
       <c r="B19" t="n">
-        <v>8984.334163013978</v>
-      </c>
-      <c r="C19" t="n">
-        <v>6766.452198194273</v>
-      </c>
-      <c r="D19" t="n">
-        <v>11202.21612783368</v>
-      </c>
-      <c r="E19" t="n">
-        <v>5588.202404383805</v>
-      </c>
-      <c r="F19" t="n">
-        <v>12380.46592164415</v>
+        <v>8624.138928108432</v>
       </c>
     </row>
     <row r="20">
@@ -3266,19 +1570,7 @@
         <v>46569</v>
       </c>
       <c r="B20" t="n">
-        <v>10132.76347228804</v>
-      </c>
-      <c r="C20" t="n">
-        <v>7914.881507468339</v>
-      </c>
-      <c r="D20" t="n">
-        <v>12350.64543710775</v>
-      </c>
-      <c r="E20" t="n">
-        <v>6736.631713657871</v>
-      </c>
-      <c r="F20" t="n">
-        <v>13528.89523091822</v>
+        <v>9156.572734775444</v>
       </c>
     </row>
     <row r="21">
@@ -3286,19 +1578,7 @@
         <v>46600</v>
       </c>
       <c r="B21" t="n">
-        <v>10290.98531667444</v>
-      </c>
-      <c r="C21" t="n">
-        <v>8073.103351854736</v>
-      </c>
-      <c r="D21" t="n">
-        <v>12508.86728149415</v>
-      </c>
-      <c r="E21" t="n">
-        <v>6894.853558044268</v>
-      </c>
-      <c r="F21" t="n">
-        <v>13687.11707530462</v>
+        <v>9290.222163992099</v>
       </c>
     </row>
     <row r="22">
@@ -3306,19 +1586,7 @@
         <v>46631</v>
       </c>
       <c r="B22" t="n">
-        <v>9090.875493813739</v>
-      </c>
-      <c r="C22" t="n">
-        <v>6872.993528994033</v>
-      </c>
-      <c r="D22" t="n">
-        <v>11308.75745863344</v>
-      </c>
-      <c r="E22" t="n">
-        <v>5694.743735183565</v>
-      </c>
-      <c r="F22" t="n">
-        <v>12487.00725244391</v>
+        <v>9156.528498375686</v>
       </c>
     </row>
     <row r="23">
@@ -3326,19 +1594,7 @@
         <v>46661</v>
       </c>
       <c r="B23" t="n">
-        <v>8785.490839879225</v>
-      </c>
-      <c r="C23" t="n">
-        <v>6567.608875059519</v>
-      </c>
-      <c r="D23" t="n">
-        <v>11003.37280469893</v>
-      </c>
-      <c r="E23" t="n">
-        <v>5389.359081249051</v>
-      </c>
-      <c r="F23" t="n">
-        <v>12181.6225985094</v>
+        <v>9172.952511793879</v>
       </c>
     </row>
     <row r="24">
@@ -3346,19 +1602,7 @@
         <v>46692</v>
       </c>
       <c r="B24" t="n">
-        <v>9033.359327324257</v>
-      </c>
-      <c r="C24" t="n">
-        <v>6815.477362504551</v>
-      </c>
-      <c r="D24" t="n">
-        <v>11251.24129214396</v>
-      </c>
-      <c r="E24" t="n">
-        <v>5637.227568694083</v>
-      </c>
-      <c r="F24" t="n">
-        <v>12429.49108595443</v>
+        <v>8962.73780315259</v>
       </c>
     </row>
     <row r="25">
@@ -3366,19 +1610,7 @@
         <v>46722</v>
       </c>
       <c r="B25" t="n">
-        <v>10010.70374260557</v>
-      </c>
-      <c r="C25" t="n">
-        <v>7792.821777785861</v>
-      </c>
-      <c r="D25" t="n">
-        <v>12228.58570742527</v>
-      </c>
-      <c r="E25" t="n">
-        <v>6614.571983975393</v>
-      </c>
-      <c r="F25" t="n">
-        <v>13406.83550123574</v>
+        <v>9143.178900083829</v>
       </c>
     </row>
     <row r="26">
@@ -3386,19 +1618,7 @@
         <v>46753</v>
       </c>
       <c r="B26" t="n">
-        <v>177.0126976903564</v>
-      </c>
-      <c r="C26" t="n">
-        <v>-2040.86926712935</v>
-      </c>
-      <c r="D26" t="n">
-        <v>2394.894662510062</v>
-      </c>
-      <c r="E26" t="n">
-        <v>-3219.119060939818</v>
-      </c>
-      <c r="F26" t="n">
-        <v>3573.14445632053</v>
+        <v>8992.74384735254</v>
       </c>
     </row>
     <row r="27">
@@ -3406,19 +1626,7 @@
         <v>46784</v>
       </c>
       <c r="B27" t="n">
-        <v>4668.186971457755</v>
-      </c>
-      <c r="C27" t="n">
-        <v>2450.305006638049</v>
-      </c>
-      <c r="D27" t="n">
-        <v>6886.068936277461</v>
-      </c>
-      <c r="E27" t="n">
-        <v>1272.055212827581</v>
-      </c>
-      <c r="F27" t="n">
-        <v>8064.318730087929</v>
+        <v>9324.182072111202</v>
       </c>
     </row>
     <row r="28">
@@ -3426,19 +1634,7 @@
         <v>46813</v>
       </c>
       <c r="B28" t="n">
-        <v>8967.928706455545</v>
-      </c>
-      <c r="C28" t="n">
-        <v>6750.046741635839</v>
-      </c>
-      <c r="D28" t="n">
-        <v>11185.81067127525</v>
-      </c>
-      <c r="E28" t="n">
-        <v>5571.796947825371</v>
-      </c>
-      <c r="F28" t="n">
-        <v>12364.06046508572</v>
+        <v>8973.800502007072</v>
       </c>
     </row>
     <row r="29">
@@ -3446,19 +1642,7 @@
         <v>46844</v>
       </c>
       <c r="B29" t="n">
-        <v>8470.604441879652</v>
-      </c>
-      <c r="C29" t="n">
-        <v>6252.722477059946</v>
-      </c>
-      <c r="D29" t="n">
-        <v>10688.48640669936</v>
-      </c>
-      <c r="E29" t="n">
-        <v>5074.472683249478</v>
-      </c>
-      <c r="F29" t="n">
-        <v>11866.73620050983</v>
+        <v>8939.725036524787</v>
       </c>
     </row>
     <row r="30">
@@ -3466,19 +1650,7 @@
         <v>46874</v>
       </c>
       <c r="B30" t="n">
-        <v>8858.15262010685</v>
-      </c>
-      <c r="C30" t="n">
-        <v>6640.270655287144</v>
-      </c>
-      <c r="D30" t="n">
-        <v>11076.03458492656</v>
-      </c>
-      <c r="E30" t="n">
-        <v>5462.020861476676</v>
-      </c>
-      <c r="F30" t="n">
-        <v>12254.28437873702</v>
+        <v>8803.98193667626</v>
       </c>
     </row>
     <row r="31">
@@ -3486,19 +1658,7 @@
         <v>46905</v>
       </c>
       <c r="B31" t="n">
-        <v>9381.430093956798</v>
-      </c>
-      <c r="C31" t="n">
-        <v>7163.548129137092</v>
-      </c>
-      <c r="D31" t="n">
-        <v>11599.3120587765</v>
-      </c>
-      <c r="E31" t="n">
-        <v>5985.298335326625</v>
-      </c>
-      <c r="F31" t="n">
-        <v>12777.56185258697</v>
+        <v>9013.692857679825</v>
       </c>
     </row>
     <row r="32">
@@ -3506,19 +1666,7 @@
         <v>46935</v>
       </c>
       <c r="B32" t="n">
-        <v>10578.97499333131</v>
-      </c>
-      <c r="C32" t="n">
-        <v>8361.093028511606</v>
-      </c>
-      <c r="D32" t="n">
-        <v>12796.85695815102</v>
-      </c>
-      <c r="E32" t="n">
-        <v>7182.843234701138</v>
-      </c>
-      <c r="F32" t="n">
-        <v>13975.10675196149</v>
+        <v>9534.867580279346</v>
       </c>
     </row>
     <row r="33">
@@ -3526,19 +1674,7 @@
         <v>46966</v>
       </c>
       <c r="B33" t="n">
-        <v>10742.50742052149</v>
-      </c>
-      <c r="C33" t="n">
-        <v>8524.625455701786</v>
-      </c>
-      <c r="D33" t="n">
-        <v>12960.3893853412</v>
-      </c>
-      <c r="E33" t="n">
-        <v>7346.375661891318</v>
-      </c>
-      <c r="F33" t="n">
-        <v>14138.63917915167</v>
+        <v>9669.073045312685</v>
       </c>
     </row>
     <row r="34">
@@ -3546,19 +1682,7 @@
         <v>46997</v>
       </c>
       <c r="B34" t="n">
-        <v>9488.289121678165</v>
-      </c>
-      <c r="C34" t="n">
-        <v>7270.407156858459</v>
-      </c>
-      <c r="D34" t="n">
-        <v>11706.17108649787</v>
-      </c>
-      <c r="E34" t="n">
-        <v>6092.157363047991</v>
-      </c>
-      <c r="F34" t="n">
-        <v>12884.42088030834</v>
+        <v>9549.485700754429</v>
       </c>
     </row>
     <row r="35">
@@ -3566,19 +1690,7 @@
         <v>47027</v>
       </c>
       <c r="B35" t="n">
-        <v>9168.160321752344</v>
-      </c>
-      <c r="C35" t="n">
-        <v>6950.278356932638</v>
-      </c>
-      <c r="D35" t="n">
-        <v>11386.04228657205</v>
-      </c>
-      <c r="E35" t="n">
-        <v>5772.02856312217</v>
-      </c>
-      <c r="F35" t="n">
-        <v>12564.29208038252</v>
+        <v>9569.936878792583</v>
       </c>
     </row>
     <row r="36">
@@ -3586,19 +1698,7 @@
         <v>47058</v>
       </c>
       <c r="B36" t="n">
-        <v>9425.402195809222</v>
-      </c>
-      <c r="C36" t="n">
-        <v>7207.520230989516</v>
-      </c>
-      <c r="D36" t="n">
-        <v>11643.28416062893</v>
-      </c>
-      <c r="E36" t="n">
-        <v>6029.270437179048</v>
-      </c>
-      <c r="F36" t="n">
-        <v>12821.5339544394</v>
+        <v>9359.717576478124</v>
       </c>
     </row>
     <row r="37">
@@ -3606,19 +1706,7 @@
         <v>47088</v>
       </c>
       <c r="B37" t="n">
-        <v>10443.59721400618</v>
-      </c>
-      <c r="C37" t="n">
-        <v>8225.715249186476</v>
-      </c>
-      <c r="D37" t="n">
-        <v>12661.47917882589</v>
-      </c>
-      <c r="E37" t="n">
-        <v>7047.465455376008</v>
-      </c>
-      <c r="F37" t="n">
-        <v>13839.72897263636</v>
+        <v>9531.210109152671</v>
       </c>
     </row>
     <row r="38">
@@ -3626,19 +1714,7 @@
         <v>47119</v>
       </c>
       <c r="B38" t="n">
-        <v>184.6397836746158</v>
-      </c>
-      <c r="C38" t="n">
-        <v>-2033.24218114509</v>
-      </c>
-      <c r="D38" t="n">
-        <v>2402.521748494322</v>
-      </c>
-      <c r="E38" t="n">
-        <v>-3211.491974955558</v>
-      </c>
-      <c r="F38" t="n">
-        <v>3580.77154230479</v>
+        <v>9383.054673974115</v>
       </c>
     </row>
     <row r="39">
@@ -3646,19 +1722,7 @@
         <v>47150</v>
       </c>
       <c r="B39" t="n">
-        <v>4868.609186525874</v>
-      </c>
-      <c r="C39" t="n">
-        <v>2650.727221706168</v>
-      </c>
-      <c r="D39" t="n">
-        <v>7086.49115134558</v>
-      </c>
-      <c r="E39" t="n">
-        <v>1472.4774278957</v>
-      </c>
-      <c r="F39" t="n">
-        <v>8264.740945156049</v>
+        <v>9715.90955293407</v>
       </c>
     </row>
     <row r="40">
@@ -3666,19 +1730,7 @@
         <v>47178</v>
       </c>
       <c r="B40" t="n">
-        <v>9351.581809856145</v>
-      </c>
-      <c r="C40" t="n">
-        <v>7133.699845036439</v>
-      </c>
-      <c r="D40" t="n">
-        <v>11569.46377467585</v>
-      </c>
-      <c r="E40" t="n">
-        <v>5955.450051225971</v>
-      </c>
-      <c r="F40" t="n">
-        <v>12747.71356848632</v>
+        <v>9365.067952448193</v>
       </c>
     </row>
     <row r="41">
@@ -3686,19 +1738,7 @@
         <v>47209</v>
       </c>
       <c r="B41" t="n">
-        <v>8831.694426723901</v>
-      </c>
-      <c r="C41" t="n">
-        <v>6613.812461904196</v>
-      </c>
-      <c r="D41" t="n">
-        <v>11049.57639154361</v>
-      </c>
-      <c r="E41" t="n">
-        <v>5435.562668093728</v>
-      </c>
-      <c r="F41" t="n">
-        <v>12227.82618535408</v>
+        <v>9329.972563529209</v>
       </c>
     </row>
     <row r="42">
@@ -3706,19 +1746,7 @@
         <v>47239</v>
       </c>
       <c r="B42" t="n">
-        <v>9234.426570914657</v>
-      </c>
-      <c r="C42" t="n">
-        <v>7016.544606094951</v>
-      </c>
-      <c r="D42" t="n">
-        <v>11452.30853573436</v>
-      </c>
-      <c r="E42" t="n">
-        <v>5838.294812284483</v>
-      </c>
-      <c r="F42" t="n">
-        <v>12630.55832954483</v>
+        <v>9194.890786278616</v>
       </c>
     </row>
     <row r="43">
@@ -3726,19 +1754,7 @@
         <v>47270</v>
       </c>
       <c r="B43" t="n">
-        <v>9778.52602489962</v>
-      </c>
-      <c r="C43" t="n">
-        <v>7560.644060079914</v>
-      </c>
-      <c r="D43" t="n">
-        <v>11996.40798971933</v>
-      </c>
-      <c r="E43" t="n">
-        <v>6382.394266269446</v>
-      </c>
-      <c r="F43" t="n">
-        <v>13174.65778352979</v>
+        <v>9405.216409363018</v>
       </c>
     </row>
     <row r="44">
@@ -3746,19 +1762,7 @@
         <v>47300</v>
       </c>
       <c r="B44" t="n">
-        <v>11025.18651437458</v>
-      </c>
-      <c r="C44" t="n">
-        <v>8807.304549554874</v>
-      </c>
-      <c r="D44" t="n">
-        <v>13243.06847919429</v>
-      </c>
-      <c r="E44" t="n">
-        <v>7629.054755744406</v>
-      </c>
-      <c r="F44" t="n">
-        <v>14421.31827300475</v>
+        <v>9927.671230099691</v>
       </c>
     </row>
     <row r="45">
@@ -3766,19 +1770,7 @@
         <v>47331</v>
       </c>
       <c r="B45" t="n">
-        <v>11194.02952436854</v>
-      </c>
-      <c r="C45" t="n">
-        <v>8976.147559548835</v>
-      </c>
-      <c r="D45" t="n">
-        <v>13411.91148918825</v>
-      </c>
-      <c r="E45" t="n">
-        <v>7797.897765738368</v>
-      </c>
-      <c r="F45" t="n">
-        <v>14590.16128299872</v>
+        <v>10061.81347681004</v>
       </c>
     </row>
     <row r="46">
@@ -3786,19 +1778,7 @@
         <v>47362</v>
       </c>
       <c r="B46" t="n">
-        <v>9885.702749542592</v>
-      </c>
-      <c r="C46" t="n">
-        <v>7667.820784722886</v>
-      </c>
-      <c r="D46" t="n">
-        <v>12103.5847143623</v>
-      </c>
-      <c r="E46" t="n">
-        <v>6489.570990912418</v>
-      </c>
-      <c r="F46" t="n">
-        <v>13281.83450817277</v>
+        <v>9940.622318371334</v>
       </c>
     </row>
     <row r="47">
@@ -3806,19 +1786,7 @@
         <v>47392</v>
       </c>
       <c r="B47" t="n">
-        <v>9550.829803625466</v>
-      </c>
-      <c r="C47" t="n">
-        <v>7332.94783880576</v>
-      </c>
-      <c r="D47" t="n">
-        <v>11768.71176844517</v>
-      </c>
-      <c r="E47" t="n">
-        <v>6154.698044995292</v>
-      </c>
-      <c r="F47" t="n">
-        <v>12946.96156225564</v>
+        <v>9960.615629153403</v>
       </c>
     </row>
     <row r="48">
@@ -3826,19 +1794,7 @@
         <v>47423</v>
       </c>
       <c r="B48" t="n">
-        <v>9817.445064294183</v>
-      </c>
-      <c r="C48" t="n">
-        <v>7599.563099474477</v>
-      </c>
-      <c r="D48" t="n">
-        <v>12035.32702911389</v>
-      </c>
-      <c r="E48" t="n">
-        <v>6421.313305664009</v>
-      </c>
-      <c r="F48" t="n">
-        <v>13213.57682292436</v>
+        <v>9750.396849115217</v>
       </c>
     </row>
     <row r="49">
@@ -3846,19 +1802,7 @@
         <v>47453</v>
       </c>
       <c r="B49" t="n">
-        <v>10876.4906854068</v>
-      </c>
-      <c r="C49" t="n">
-        <v>8658.608720587095</v>
-      </c>
-      <c r="D49" t="n">
-        <v>13094.37265022651</v>
-      </c>
-      <c r="E49" t="n">
-        <v>7480.358926776627</v>
-      </c>
-      <c r="F49" t="n">
-        <v>14272.62244403698</v>
+        <v>9922.90678608007</v>
       </c>
     </row>
     <row r="50">
@@ -3866,19 +1810,7 @@
         <v>47484</v>
       </c>
       <c r="B50" t="n">
-        <v>192.2668696588752</v>
-      </c>
-      <c r="C50" t="n">
-        <v>-2025.615095160831</v>
-      </c>
-      <c r="D50" t="n">
-        <v>2410.148834478581</v>
-      </c>
-      <c r="E50" t="n">
-        <v>-3203.864888971299</v>
-      </c>
-      <c r="F50" t="n">
-        <v>3588.39862828905</v>
+        <v>9774.492170477495</v>
       </c>
     </row>
     <row r="51">
@@ -3886,19 +1818,7 @@
         <v>47515</v>
       </c>
       <c r="B51" t="n">
-        <v>5069.031401593992</v>
-      </c>
-      <c r="C51" t="n">
-        <v>2851.149436774286</v>
-      </c>
-      <c r="D51" t="n">
-        <v>7286.913366413698</v>
-      </c>
-      <c r="E51" t="n">
-        <v>1672.899642963818</v>
-      </c>
-      <c r="F51" t="n">
-        <v>8465.163160224167</v>
+        <v>10107.18598336909</v>
       </c>
     </row>
     <row r="52">
@@ -3906,19 +1826,7 @@
         <v>47543</v>
       </c>
       <c r="B52" t="n">
-        <v>9735.234913256743</v>
-      </c>
-      <c r="C52" t="n">
-        <v>7517.352948437037</v>
-      </c>
-      <c r="D52" t="n">
-        <v>11953.11687807645</v>
-      </c>
-      <c r="E52" t="n">
-        <v>6339.103154626569</v>
-      </c>
-      <c r="F52" t="n">
-        <v>13131.36667188692</v>
+        <v>9756.396685897489</v>
       </c>
     </row>
     <row r="53">
@@ -3926,19 +1834,7 @@
         <v>47574</v>
       </c>
       <c r="B53" t="n">
-        <v>9192.784411568149</v>
-      </c>
-      <c r="C53" t="n">
-        <v>6974.902446748443</v>
-      </c>
-      <c r="D53" t="n">
-        <v>11410.66637638786</v>
-      </c>
-      <c r="E53" t="n">
-        <v>5796.652652937975</v>
-      </c>
-      <c r="F53" t="n">
-        <v>12588.91617019832</v>
+        <v>9721.4172568633</v>
       </c>
     </row>
     <row r="54">
@@ -3946,19 +1842,7 @@
         <v>47604</v>
       </c>
       <c r="B54" t="n">
-        <v>9610.700521722463</v>
-      </c>
-      <c r="C54" t="n">
-        <v>7392.818556902757</v>
-      </c>
-      <c r="D54" t="n">
-        <v>11828.58248654217</v>
-      </c>
-      <c r="E54" t="n">
-        <v>6214.568763092289</v>
-      </c>
-      <c r="F54" t="n">
-        <v>13006.83228035264</v>
+        <v>9586.260290741162</v>
       </c>
     </row>
     <row r="55">
@@ -3966,19 +1850,7 @@
         <v>47635</v>
       </c>
       <c r="B55" t="n">
-        <v>10175.62195584244</v>
-      </c>
-      <c r="C55" t="n">
-        <v>7957.739991022736</v>
-      </c>
-      <c r="D55" t="n">
-        <v>12393.50392066215</v>
-      </c>
-      <c r="E55" t="n">
-        <v>6779.490197212268</v>
-      </c>
-      <c r="F55" t="n">
-        <v>13571.75371447262</v>
+        <v>9796.516025459523</v>
       </c>
     </row>
     <row r="56">
@@ -3986,19 +1858,7 @@
         <v>47665</v>
       </c>
       <c r="B56" t="n">
-        <v>11471.39803541785</v>
-      </c>
-      <c r="C56" t="n">
-        <v>9253.51607059814</v>
-      </c>
-      <c r="D56" t="n">
-        <v>13689.28000023755</v>
-      </c>
-      <c r="E56" t="n">
-        <v>8075.266276787672</v>
-      </c>
-      <c r="F56" t="n">
-        <v>14867.52979404802</v>
+        <v>10318.825305828</v>
       </c>
     </row>
     <row r="57">
@@ -4006,19 +1866,7 @@
         <v>47696</v>
       </c>
       <c r="B57" t="n">
-        <v>11645.55162821559</v>
-      </c>
-      <c r="C57" t="n">
-        <v>9427.669663395885</v>
-      </c>
-      <c r="D57" t="n">
-        <v>13863.4335930353</v>
-      </c>
-      <c r="E57" t="n">
-        <v>8249.419869585417</v>
-      </c>
-      <c r="F57" t="n">
-        <v>15041.68338684577</v>
+        <v>10452.97474012635</v>
       </c>
     </row>
     <row r="58">
@@ -4026,19 +1874,7 @@
         <v>47727</v>
       </c>
       <c r="B58" t="n">
-        <v>10283.11637740702</v>
-      </c>
-      <c r="C58" t="n">
-        <v>8065.234412587313</v>
-      </c>
-      <c r="D58" t="n">
-        <v>12500.99834222673</v>
-      </c>
-      <c r="E58" t="n">
-        <v>6886.984618776845</v>
-      </c>
-      <c r="F58" t="n">
-        <v>13679.24813603719</v>
+        <v>10331.96592681877</v>
       </c>
     </row>
     <row r="59">
@@ -4046,19 +1882,7 @@
         <v>47757</v>
       </c>
       <c r="B59" t="n">
-        <v>9933.499285498583</v>
-      </c>
-      <c r="C59" t="n">
-        <v>7715.617320678877</v>
-      </c>
-      <c r="D59" t="n">
-        <v>12151.38125031829</v>
-      </c>
-      <c r="E59" t="n">
-        <v>6537.367526868409</v>
-      </c>
-      <c r="F59" t="n">
-        <v>13329.63104412876</v>
+        <v>10352.0112946792</v>
       </c>
     </row>
     <row r="60">
@@ -4066,19 +1890,7 @@
         <v>47788</v>
       </c>
       <c r="B60" t="n">
-        <v>10209.48793277915</v>
-      </c>
-      <c r="C60" t="n">
-        <v>7991.60596795944</v>
-      </c>
-      <c r="D60" t="n">
-        <v>12427.36989759885</v>
-      </c>
-      <c r="E60" t="n">
-        <v>6813.356174148972</v>
-      </c>
-      <c r="F60" t="n">
-        <v>13605.61969140932</v>
+        <v>10141.79245526097</v>
       </c>
     </row>
     <row r="61">
@@ -4086,19 +1898,7 @@
         <v>47818</v>
       </c>
       <c r="B61" t="n">
-        <v>11309.38415680742</v>
-      </c>
-      <c r="C61" t="n">
-        <v>9091.502191987714</v>
-      </c>
-      <c r="D61" t="n">
-        <v>13527.26612162713</v>
-      </c>
-      <c r="E61" t="n">
-        <v>7913.252398177247</v>
-      </c>
-      <c r="F61" t="n">
-        <v>14705.51591543759</v>
+        <v>10314.18671875461</v>
       </c>
     </row>
     <row r="62">
@@ -4106,19 +1906,7 @@
         <v>47849</v>
       </c>
       <c r="B62" t="n">
-        <v>199.8939556431346</v>
-      </c>
-      <c r="C62" t="n">
-        <v>-2017.988009176571</v>
-      </c>
-      <c r="D62" t="n">
-        <v>2417.775920462841</v>
-      </c>
-      <c r="E62" t="n">
-        <v>-3196.23780298704</v>
-      </c>
-      <c r="F62" t="n">
-        <v>3596.025714273309</v>
+        <v>10165.80157059149</v>
       </c>
     </row>
     <row r="63">
@@ -4126,19 +1914,7 @@
         <v>47880</v>
       </c>
       <c r="B63" t="n">
-        <v>5269.453616662111</v>
-      </c>
-      <c r="C63" t="n">
-        <v>3051.571651842405</v>
-      </c>
-      <c r="D63" t="n">
-        <v>7487.335581481817</v>
-      </c>
-      <c r="E63" t="n">
-        <v>1873.321858031937</v>
-      </c>
-      <c r="F63" t="n">
-        <v>8665.585375292285</v>
+        <v>10498.51369584071</v>
       </c>
     </row>
     <row r="64">
@@ -4146,19 +1922,7 @@
         <v>47908</v>
       </c>
       <c r="B64" t="n">
-        <v>10118.88801665734</v>
-      </c>
-      <c r="C64" t="n">
-        <v>7901.006051837638</v>
-      </c>
-      <c r="D64" t="n">
-        <v>12336.76998147705</v>
-      </c>
-      <c r="E64" t="n">
-        <v>6722.75625802717</v>
-      </c>
-      <c r="F64" t="n">
-        <v>13515.01977528752</v>
+        <v>10147.71845179382</v>
       </c>
     </row>
     <row r="65">
@@ -4166,19 +1930,7 @@
         <v>47939</v>
       </c>
       <c r="B65" t="n">
-        <v>9553.874396412397</v>
-      </c>
-      <c r="C65" t="n">
-        <v>7335.992431592691</v>
-      </c>
-      <c r="D65" t="n">
-        <v>11771.7563612321</v>
-      </c>
-      <c r="E65" t="n">
-        <v>6157.742637782223</v>
-      </c>
-      <c r="F65" t="n">
-        <v>12950.00615504257</v>
+        <v>10112.72583873581</v>
       </c>
     </row>
     <row r="66">
@@ -4186,19 +1938,7 @@
         <v>47969</v>
       </c>
       <c r="B66" t="n">
-        <v>9986.97447253027</v>
-      </c>
-      <c r="C66" t="n">
-        <v>7769.092507710564</v>
-      </c>
-      <c r="D66" t="n">
-        <v>12204.85643734998</v>
-      </c>
-      <c r="E66" t="n">
-        <v>6590.842713900096</v>
-      </c>
-      <c r="F66" t="n">
-        <v>13383.10623116044</v>
+        <v>9977.577421189544</v>
       </c>
     </row>
     <row r="67">
@@ -4206,19 +1946,7 @@
         <v>48000</v>
       </c>
       <c r="B67" t="n">
-        <v>10572.71788678526</v>
-      </c>
-      <c r="C67" t="n">
-        <v>8354.835921965556</v>
-      </c>
-      <c r="D67" t="n">
-        <v>12790.59985160497</v>
-      </c>
-      <c r="E67" t="n">
-        <v>7176.586128155088</v>
-      </c>
-      <c r="F67" t="n">
-        <v>13968.84964541544</v>
+        <v>10187.84110184442</v>
       </c>
     </row>
     <row r="68">
@@ -4226,19 +1954,7 @@
         <v>48030</v>
       </c>
       <c r="B68" t="n">
-        <v>11917.60955646111</v>
-      </c>
-      <c r="C68" t="n">
-        <v>9699.727591641407</v>
-      </c>
-      <c r="D68" t="n">
-        <v>14135.49152128082</v>
-      </c>
-      <c r="E68" t="n">
-        <v>8521.477797830939</v>
-      </c>
-      <c r="F68" t="n">
-        <v>15313.74131509129</v>
+        <v>10710.16692938077</v>
       </c>
     </row>
     <row r="69">
@@ -4246,19 +1962,7 @@
         <v>48061</v>
       </c>
       <c r="B69" t="n">
-        <v>12097.07373206264</v>
-      </c>
-      <c r="C69" t="n">
-        <v>9879.191767242937</v>
-      </c>
-      <c r="D69" t="n">
-        <v>14314.95569688235</v>
-      </c>
-      <c r="E69" t="n">
-        <v>8700.941973432469</v>
-      </c>
-      <c r="F69" t="n">
-        <v>15493.20549069282</v>
+        <v>10844.31554648849</v>
       </c>
     </row>
     <row r="70">
@@ -4266,19 +1970,7 @@
         <v>48092</v>
       </c>
       <c r="B70" t="n">
-        <v>10680.53000527145</v>
-      </c>
-      <c r="C70" t="n">
-        <v>8462.648040451741</v>
-      </c>
-      <c r="D70" t="n">
-        <v>12898.41197009115</v>
-      </c>
-      <c r="E70" t="n">
-        <v>7284.398246641273</v>
-      </c>
-      <c r="F70" t="n">
-        <v>14076.66176390162</v>
+        <v>10723.28600150671</v>
       </c>
     </row>
     <row r="71">
@@ -4286,19 +1978,7 @@
         <v>48122</v>
       </c>
       <c r="B71" t="n">
-        <v>10316.1687673717</v>
-      </c>
-      <c r="C71" t="n">
-        <v>8098.286802551998</v>
-      </c>
-      <c r="D71" t="n">
-        <v>12534.05073219141</v>
-      </c>
-      <c r="E71" t="n">
-        <v>6920.03700874153</v>
-      </c>
-      <c r="F71" t="n">
-        <v>13712.30052600188</v>
+        <v>10743.32545075346</v>
       </c>
     </row>
     <row r="72">
@@ -4306,19 +1986,7 @@
         <v>48153</v>
       </c>
       <c r="B72" t="n">
-        <v>10601.53080126411</v>
-      </c>
-      <c r="C72" t="n">
-        <v>8383.648836444405</v>
-      </c>
-      <c r="D72" t="n">
-        <v>12819.41276608382</v>
-      </c>
-      <c r="E72" t="n">
-        <v>7205.399042633937</v>
-      </c>
-      <c r="F72" t="n">
-        <v>13997.66255989428</v>
+        <v>10533.10661808642</v>
       </c>
     </row>
     <row r="73">
@@ -4326,19 +1994,7 @@
         <v>48183</v>
       </c>
       <c r="B73" t="n">
-        <v>11742.27762820804</v>
-      </c>
-      <c r="C73" t="n">
-        <v>9524.39566338833</v>
-      </c>
-      <c r="D73" t="n">
-        <v>13960.15959302774</v>
-      </c>
-      <c r="E73" t="n">
-        <v>8346.145869577862</v>
-      </c>
-      <c r="F73" t="n">
-        <v>15138.40938683821</v>
+        <v>10705.51403304018</v>
       </c>
     </row>
     <row r="74">
@@ -4346,19 +2002,7 @@
         <v>48214</v>
       </c>
       <c r="B74" t="n">
-        <v>207.521041627394</v>
-      </c>
-      <c r="C74" t="n">
-        <v>-2010.360923192312</v>
-      </c>
-      <c r="D74" t="n">
-        <v>2425.4030064471</v>
-      </c>
-      <c r="E74" t="n">
-        <v>-3188.61071700278</v>
-      </c>
-      <c r="F74" t="n">
-        <v>3603.652800257568</v>
+        <v>10557.12553458549</v>
       </c>
     </row>
     <row r="75">
@@ -4366,19 +2010,7 @@
         <v>48245</v>
       </c>
       <c r="B75" t="n">
-        <v>5469.87583173023</v>
-      </c>
-      <c r="C75" t="n">
-        <v>3251.993866910524</v>
-      </c>
-      <c r="D75" t="n">
-        <v>7687.757796549936</v>
-      </c>
-      <c r="E75" t="n">
-        <v>2073.744073100056</v>
-      </c>
-      <c r="F75" t="n">
-        <v>8866.007590360405</v>
+        <v>10889.83557781679</v>
       </c>
     </row>
     <row r="76">
@@ -4386,19 +2018,7 @@
         <v>48274</v>
       </c>
       <c r="B76" t="n">
-        <v>10502.54112005794</v>
-      </c>
-      <c r="C76" t="n">
-        <v>8284.659155238236</v>
-      </c>
-      <c r="D76" t="n">
-        <v>12720.42308487765</v>
-      </c>
-      <c r="E76" t="n">
-        <v>7106.409361427768</v>
-      </c>
-      <c r="F76" t="n">
-        <v>13898.67287868812</v>
+        <v>10539.04100986396</v>
       </c>
     </row>
     <row r="77">
@@ -4406,19 +2026,7 @@
         <v>48305</v>
       </c>
       <c r="B77" t="n">
-        <v>9914.964381256645</v>
-      </c>
-      <c r="C77" t="n">
-        <v>7697.082416436939</v>
-      </c>
-      <c r="D77" t="n">
-        <v>12132.84634607635</v>
-      </c>
-      <c r="E77" t="n">
-        <v>6518.832622626471</v>
-      </c>
-      <c r="F77" t="n">
-        <v>13311.09613988682</v>
+        <v>10504.04989575953</v>
       </c>
     </row>
     <row r="78">
@@ -4426,19 +2034,7 @@
         <v>48335</v>
       </c>
       <c r="B78" t="n">
-        <v>10363.24842333808</v>
-      </c>
-      <c r="C78" t="n">
-        <v>8145.366458518372</v>
-      </c>
-      <c r="D78" t="n">
-        <v>12581.13038815778</v>
-      </c>
-      <c r="E78" t="n">
-        <v>6967.116664707904</v>
-      </c>
-      <c r="F78" t="n">
-        <v>13759.38018196825</v>
+        <v>10368.90050628553</v>
       </c>
     </row>
     <row r="79">
@@ -4446,19 +2042,7 @@
         <v>48366</v>
       </c>
       <c r="B79" t="n">
-        <v>10969.81381772808</v>
-      </c>
-      <c r="C79" t="n">
-        <v>8751.931852908376</v>
-      </c>
-      <c r="D79" t="n">
-        <v>13187.69578254779</v>
-      </c>
-      <c r="E79" t="n">
-        <v>7573.682059097908</v>
-      </c>
-      <c r="F79" t="n">
-        <v>14365.94557635826</v>
+        <v>10579.16328352957</v>
       </c>
     </row>
     <row r="80">
@@ -4466,19 +2050,7 @@
         <v>48396</v>
       </c>
       <c r="B80" t="n">
-        <v>12363.82107750438</v>
-      </c>
-      <c r="C80" t="n">
-        <v>10145.93911268467</v>
-      </c>
-      <c r="D80" t="n">
-        <v>14581.70304232409</v>
-      </c>
-      <c r="E80" t="n">
-        <v>8967.689318874207</v>
-      </c>
-      <c r="F80" t="n">
-        <v>15759.95283613455</v>
+        <v>11101.48722974071</v>
       </c>
     </row>
     <row r="81">
@@ -4486,19 +2058,7 @@
         <v>48427</v>
       </c>
       <c r="B81" t="n">
-        <v>12548.59583590969</v>
-      </c>
-      <c r="C81" t="n">
-        <v>10330.71387108999</v>
-      </c>
-      <c r="D81" t="n">
-        <v>14766.4778007294</v>
-      </c>
-      <c r="E81" t="n">
-        <v>9152.464077279519</v>
-      </c>
-      <c r="F81" t="n">
-        <v>15944.72759453987</v>
+        <v>11235.63593975867</v>
       </c>
     </row>
     <row r="82">
@@ -4506,19 +2066,7 @@
         <v>48458</v>
       </c>
       <c r="B82" t="n">
-        <v>11077.94363313587</v>
-      </c>
-      <c r="C82" t="n">
-        <v>8860.061668316166</v>
-      </c>
-      <c r="D82" t="n">
-        <v>13295.82559795558</v>
-      </c>
-      <c r="E82" t="n">
-        <v>7681.811874505698</v>
-      </c>
-      <c r="F82" t="n">
-        <v>14474.07539176605</v>
+        <v>11114.60875185828</v>
       </c>
     </row>
     <row r="83">
@@ -4526,19 +2074,7 @@
         <v>48488</v>
       </c>
       <c r="B83" t="n">
-        <v>10698.83824924482</v>
-      </c>
-      <c r="C83" t="n">
-        <v>8480.956284425118</v>
-      </c>
-      <c r="D83" t="n">
-        <v>12916.72021406453</v>
-      </c>
-      <c r="E83" t="n">
-        <v>7302.70649061465</v>
-      </c>
-      <c r="F83" t="n">
-        <v>14094.970007875</v>
+        <v>11134.64887402001</v>
       </c>
     </row>
     <row r="84">
@@ -4546,19 +2082,7 @@
         <v>48519</v>
       </c>
       <c r="B84" t="n">
-        <v>10993.57366974907</v>
-      </c>
-      <c r="C84" t="n">
-        <v>8775.691704929368</v>
-      </c>
-      <c r="D84" t="n">
-        <v>13211.45563456878</v>
-      </c>
-      <c r="E84" t="n">
-        <v>7597.4419111189</v>
-      </c>
-      <c r="F84" t="n">
-        <v>14389.70542837925</v>
+        <v>10924.4300405854</v>
       </c>
     </row>
     <row r="85">
@@ -4566,19 +2090,7 @@
         <v>48549</v>
       </c>
       <c r="B85" t="n">
-        <v>12175.17109960865</v>
-      </c>
-      <c r="C85" t="n">
-        <v>9957.289134788949</v>
-      </c>
-      <c r="D85" t="n">
-        <v>14393.05306442836</v>
-      </c>
-      <c r="E85" t="n">
-        <v>8779.039340978481</v>
-      </c>
-      <c r="F85" t="n">
-        <v>15571.30285823883</v>
+        <v>11096.8359602879</v>
       </c>
     </row>
     <row r="86">
@@ -4586,19 +2098,7 @@
         <v>48580</v>
       </c>
       <c r="B86" t="n">
-        <v>215.1481276116534</v>
-      </c>
-      <c r="C86" t="n">
-        <v>-2002.733837208053</v>
-      </c>
-      <c r="D86" t="n">
-        <v>2433.030092431359</v>
-      </c>
-      <c r="E86" t="n">
-        <v>-3180.983631018521</v>
-      </c>
-      <c r="F86" t="n">
-        <v>3611.279886241828</v>
+        <v>10948.44784274359</v>
       </c>
     </row>
     <row r="87">
@@ -4606,19 +2106,7 @@
         <v>48611</v>
       </c>
       <c r="B87" t="n">
-        <v>5670.298046798349</v>
-      </c>
-      <c r="C87" t="n">
-        <v>3452.416081978643</v>
-      </c>
-      <c r="D87" t="n">
-        <v>7888.180011618055</v>
-      </c>
-      <c r="E87" t="n">
-        <v>2274.166288168175</v>
-      </c>
-      <c r="F87" t="n">
-        <v>9066.429805428523</v>
+        <v>11281.15812268928</v>
       </c>
     </row>
     <row r="88">
@@ -4626,19 +2114,7 @@
         <v>48639</v>
       </c>
       <c r="B88" t="n">
-        <v>10886.19422345854</v>
-      </c>
-      <c r="C88" t="n">
-        <v>8668.312258638834</v>
-      </c>
-      <c r="D88" t="n">
-        <v>13104.07618827825</v>
-      </c>
-      <c r="E88" t="n">
-        <v>7490.062464828367</v>
-      </c>
-      <c r="F88" t="n">
-        <v>14282.32598208871</v>
+        <v>10930.36347786815</v>
       </c>
     </row>
     <row r="89">
@@ -4646,19 +2122,7 @@
         <v>48670</v>
       </c>
       <c r="B89" t="n">
-        <v>10276.05436610089</v>
-      </c>
-      <c r="C89" t="n">
-        <v>8058.172401281188</v>
-      </c>
-      <c r="D89" t="n">
-        <v>12493.9363309206</v>
-      </c>
-      <c r="E89" t="n">
-        <v>6879.92260747072</v>
-      </c>
-      <c r="F89" t="n">
-        <v>13672.18612473107</v>
+        <v>10895.37219334065</v>
       </c>
     </row>
     <row r="90">
@@ -4666,19 +2130,7 @@
         <v>48700</v>
       </c>
       <c r="B90" t="n">
-        <v>10739.52237414588</v>
-      </c>
-      <c r="C90" t="n">
-        <v>8521.640409326179</v>
-      </c>
-      <c r="D90" t="n">
-        <v>12957.40433896559</v>
-      </c>
-      <c r="E90" t="n">
-        <v>7343.390615515711</v>
-      </c>
-      <c r="F90" t="n">
-        <v>14135.65413277606</v>
+        <v>10760.22291436967</v>
       </c>
     </row>
     <row r="91">
@@ -4686,19 +2138,7 @@
         <v>48731</v>
       </c>
       <c r="B91" t="n">
-        <v>11366.9097486709</v>
-      </c>
-      <c r="C91" t="n">
-        <v>9149.027783851197</v>
-      </c>
-      <c r="D91" t="n">
-        <v>13584.79171349061</v>
-      </c>
-      <c r="E91" t="n">
-        <v>7970.777990040729</v>
-      </c>
-      <c r="F91" t="n">
-        <v>14763.04150730108</v>
+        <v>10970.48579432673</v>
       </c>
     </row>
     <row r="92">
@@ -4706,19 +2146,7 @@
         <v>48761</v>
       </c>
       <c r="B92" t="n">
-        <v>12810.03259854765</v>
-      </c>
-      <c r="C92" t="n">
-        <v>10592.15063372794</v>
-      </c>
-      <c r="D92" t="n">
-        <v>15027.91456336735</v>
-      </c>
-      <c r="E92" t="n">
-        <v>9413.900839917475</v>
-      </c>
-      <c r="F92" t="n">
-        <v>16206.16435717782</v>
+        <v>11492.80995443457</v>
       </c>
     </row>
     <row r="93">
@@ -4726,19 +2154,7 @@
         <v>48792</v>
       </c>
       <c r="B93" t="n">
-        <v>13000.11793975674</v>
-      </c>
-      <c r="C93" t="n">
-        <v>10782.23597493704</v>
-      </c>
-      <c r="D93" t="n">
-        <v>15217.99990457645</v>
-      </c>
-      <c r="E93" t="n">
-        <v>9603.986181126571</v>
-      </c>
-      <c r="F93" t="n">
-        <v>16396.24969838692</v>
+        <v>11626.95865388913</v>
       </c>
     </row>
     <row r="94">
@@ -4746,19 +2162,7 @@
         <v>48823</v>
       </c>
       <c r="B94" t="n">
-        <v>11475.3572610003</v>
-      </c>
-      <c r="C94" t="n">
-        <v>9257.475296180593</v>
-      </c>
-      <c r="D94" t="n">
-        <v>13693.23922582001</v>
-      </c>
-      <c r="E94" t="n">
-        <v>8079.225502370125</v>
-      </c>
-      <c r="F94" t="n">
-        <v>14871.48901963047</v>
+        <v>11505.93119800109</v>
       </c>
     </row>
     <row r="95">
@@ -4766,19 +2170,7 @@
         <v>48853</v>
       </c>
       <c r="B95" t="n">
-        <v>11081.50773111794</v>
-      </c>
-      <c r="C95" t="n">
-        <v>8863.625766298237</v>
-      </c>
-      <c r="D95" t="n">
-        <v>13299.38969593765</v>
-      </c>
-      <c r="E95" t="n">
-        <v>7685.375972487769</v>
-      </c>
-      <c r="F95" t="n">
-        <v>14477.63948974812</v>
+        <v>11525.97124365595</v>
       </c>
     </row>
     <row r="96">
@@ -4786,19 +2178,7 @@
         <v>48884</v>
       </c>
       <c r="B96" t="n">
-        <v>11385.61653823404</v>
-      </c>
-      <c r="C96" t="n">
-        <v>9167.734573414331</v>
-      </c>
-      <c r="D96" t="n">
-        <v>13603.49850305374</v>
-      </c>
-      <c r="E96" t="n">
-        <v>7989.484779603863</v>
-      </c>
-      <c r="F96" t="n">
-        <v>14781.74829686421</v>
+        <v>11315.75241030861</v>
       </c>
     </row>
     <row r="97">
@@ -4806,19 +2186,7 @@
         <v>48914</v>
       </c>
       <c r="B97" t="n">
-        <v>12608.06457100927</v>
-      </c>
-      <c r="C97" t="n">
-        <v>10390.18260618957</v>
-      </c>
-      <c r="D97" t="n">
-        <v>14825.94653582898</v>
-      </c>
-      <c r="E97" t="n">
-        <v>9211.9328123791</v>
-      </c>
-      <c r="F97" t="n">
-        <v>16004.19632963945</v>
+        <v>11488.15850001325</v>
       </c>
     </row>
     <row r="98">
@@ -4826,19 +2194,7 @@
         <v>48945</v>
       </c>
       <c r="B98" t="n">
-        <v>222.7752135959128</v>
-      </c>
-      <c r="C98" t="n">
-        <v>-1995.106751223793</v>
-      </c>
-      <c r="D98" t="n">
-        <v>2440.657178415619</v>
-      </c>
-      <c r="E98" t="n">
-        <v>-3173.356545034262</v>
-      </c>
-      <c r="F98" t="n">
-        <v>3618.906972226087</v>
+        <v>11339.77033916145</v>
       </c>
     </row>
     <row r="99">
@@ -4846,19 +2202,7 @@
         <v>48976</v>
       </c>
       <c r="B99" t="n">
-        <v>5870.720261866466</v>
-      </c>
-      <c r="C99" t="n">
-        <v>3652.83829704676</v>
-      </c>
-      <c r="D99" t="n">
-        <v>8088.602226686172</v>
-      </c>
-      <c r="E99" t="n">
-        <v>2474.588503236292</v>
-      </c>
-      <c r="F99" t="n">
-        <v>9266.852020496641</v>
+        <v>11672.48059219397</v>
       </c>
     </row>
     <row r="100">
@@ -4866,19 +2210,7 @@
         <v>49004</v>
       </c>
       <c r="B100" t="n">
-        <v>11269.84732685914</v>
-      </c>
-      <c r="C100" t="n">
-        <v>9051.965362039435</v>
-      </c>
-      <c r="D100" t="n">
-        <v>13487.72929167885</v>
-      </c>
-      <c r="E100" t="n">
-        <v>7873.715568228967</v>
-      </c>
-      <c r="F100" t="n">
-        <v>14665.97908548931</v>
+        <v>11321.68595611235</v>
       </c>
     </row>
     <row r="101">
@@ -4886,19 +2218,7 @@
         <v>49035</v>
       </c>
       <c r="B101" t="n">
-        <v>10637.14435094514</v>
-      </c>
-      <c r="C101" t="n">
-        <v>8419.262386125436</v>
-      </c>
-      <c r="D101" t="n">
-        <v>12855.02631576485</v>
-      </c>
-      <c r="E101" t="n">
-        <v>7241.012592314968</v>
-      </c>
-      <c r="F101" t="n">
-        <v>14033.27610957532</v>
+        <v>11286.69469096105</v>
       </c>
     </row>
     <row r="102">
@@ -4906,19 +2226,7 @@
         <v>49065</v>
       </c>
       <c r="B102" t="n">
-        <v>11115.79632495369</v>
-      </c>
-      <c r="C102" t="n">
-        <v>8897.914360133986</v>
-      </c>
-      <c r="D102" t="n">
-        <v>13333.6782897734</v>
-      </c>
-      <c r="E102" t="n">
-        <v>7719.664566323518</v>
-      </c>
-      <c r="F102" t="n">
-        <v>14511.92808358387</v>
+        <v>11151.54539942647</v>
       </c>
     </row>
     <row r="103">
@@ -4926,19 +2234,7 @@
         <v>49096</v>
       </c>
       <c r="B103" t="n">
-        <v>11764.00567961372</v>
-      </c>
-      <c r="C103" t="n">
-        <v>9546.123714794017</v>
-      </c>
-      <c r="D103" t="n">
-        <v>13981.88764443343</v>
-      </c>
-      <c r="E103" t="n">
-        <v>8367.873920983549</v>
-      </c>
-      <c r="F103" t="n">
-        <v>15160.1374382439</v>
+        <v>11361.80826770561</v>
       </c>
     </row>
     <row r="104">
@@ -4946,19 +2242,7 @@
         <v>49126</v>
       </c>
       <c r="B104" t="n">
-        <v>13256.24411959092</v>
-      </c>
-      <c r="C104" t="n">
-        <v>11038.36215477121</v>
-      </c>
-      <c r="D104" t="n">
-        <v>15474.12608441062</v>
-      </c>
-      <c r="E104" t="n">
-        <v>9860.112360960742</v>
-      </c>
-      <c r="F104" t="n">
-        <v>16652.37587822109</v>
+        <v>11884.13240349452</v>
       </c>
     </row>
     <row r="105">
@@ -4966,19 +2250,7 @@
         <v>49157</v>
       </c>
       <c r="B105" t="n">
-        <v>13451.64004360379</v>
-      </c>
-      <c r="C105" t="n">
-        <v>11233.75807878409</v>
-      </c>
-      <c r="D105" t="n">
-        <v>15669.5220084235</v>
-      </c>
-      <c r="E105" t="n">
-        <v>10055.50828497362</v>
-      </c>
-      <c r="F105" t="n">
-        <v>16847.77180223397</v>
+        <v>12018.28110415008</v>
       </c>
     </row>
     <row r="106">
@@ -4986,19 +2258,7 @@
         <v>49188</v>
       </c>
       <c r="B106" t="n">
-        <v>11872.77088886473</v>
-      </c>
-      <c r="C106" t="n">
-        <v>9654.888924045021</v>
-      </c>
-      <c r="D106" t="n">
-        <v>14090.65285368443</v>
-      </c>
-      <c r="E106" t="n">
-        <v>8476.639130234553</v>
-      </c>
-      <c r="F106" t="n">
-        <v>15268.9026474949</v>
+        <v>11897.25367873082</v>
       </c>
     </row>
     <row r="107">
@@ -5006,19 +2266,7 @@
         <v>49218</v>
       </c>
       <c r="B107" t="n">
-        <v>11464.17721299106</v>
-      </c>
-      <c r="C107" t="n">
-        <v>9246.295248171358</v>
-      </c>
-      <c r="D107" t="n">
-        <v>13682.05917781077</v>
-      </c>
-      <c r="E107" t="n">
-        <v>8068.04545436089</v>
-      </c>
-      <c r="F107" t="n">
-        <v>14860.30897162124</v>
+        <v>11917.29373308411</v>
       </c>
     </row>
     <row r="108">
@@ -5026,19 +2274,7 @@
         <v>49249</v>
       </c>
       <c r="B108" t="n">
-        <v>11777.659406719</v>
-      </c>
-      <c r="C108" t="n">
-        <v>9559.777441899294</v>
-      </c>
-      <c r="D108" t="n">
-        <v>13995.54137153871</v>
-      </c>
-      <c r="E108" t="n">
-        <v>8381.527648088826</v>
-      </c>
-      <c r="F108" t="n">
-        <v>15173.79116534917</v>
+        <v>11707.07489972684</v>
       </c>
     </row>
     <row r="109">
@@ -5046,19 +2282,7 @@
         <v>49279</v>
       </c>
       <c r="B109" t="n">
-        <v>13040.95804240989</v>
-      </c>
-      <c r="C109" t="n">
-        <v>10823.07607759019</v>
-      </c>
-      <c r="D109" t="n">
-        <v>15258.8400072296</v>
-      </c>
-      <c r="E109" t="n">
-        <v>9644.826283779717</v>
-      </c>
-      <c r="F109" t="n">
-        <v>16437.08980104007</v>
+        <v>11879.48097010314</v>
       </c>
     </row>
     <row r="110">
@@ -5066,19 +2290,7 @@
         <v>49310</v>
       </c>
       <c r="B110" t="n">
-        <v>230.4022995801722</v>
-      </c>
-      <c r="C110" t="n">
-        <v>-1987.479665239534</v>
-      </c>
-      <c r="D110" t="n">
-        <v>2448.284264399878</v>
-      </c>
-      <c r="E110" t="n">
-        <v>-3165.729459050002</v>
-      </c>
-      <c r="F110" t="n">
-        <v>3626.534058210347</v>
+        <v>11731.09281417517</v>
       </c>
     </row>
     <row r="111">
@@ -5086,19 +2298,7 @@
         <v>49341</v>
       </c>
       <c r="B111" t="n">
-        <v>6071.142476934585</v>
-      </c>
-      <c r="C111" t="n">
-        <v>3853.260512114879</v>
-      </c>
-      <c r="D111" t="n">
-        <v>8289.024441754291</v>
-      </c>
-      <c r="E111" t="n">
-        <v>2675.010718304411</v>
-      </c>
-      <c r="F111" t="n">
-        <v>9467.274235564759</v>
+        <v>12063.80307026758</v>
       </c>
     </row>
     <row r="112">
@@ -5106,19 +2306,7 @@
         <v>49369</v>
       </c>
       <c r="B112" t="n">
-        <v>11653.50043025974</v>
-      </c>
-      <c r="C112" t="n">
-        <v>9435.618465440035</v>
-      </c>
-      <c r="D112" t="n">
-        <v>13871.38239507945</v>
-      </c>
-      <c r="E112" t="n">
-        <v>8257.368671629567</v>
-      </c>
-      <c r="F112" t="n">
-        <v>15049.63218888991</v>
+        <v>11713.00843319233</v>
       </c>
     </row>
     <row r="113">
@@ -5126,19 +2314,7 @@
         <v>49400</v>
       </c>
       <c r="B113" t="n">
-        <v>10998.23433578939</v>
-      </c>
-      <c r="C113" t="n">
-        <v>8780.352370969684</v>
-      </c>
-      <c r="D113" t="n">
-        <v>13216.1163006091</v>
-      </c>
-      <c r="E113" t="n">
-        <v>7602.102577159216</v>
-      </c>
-      <c r="F113" t="n">
-        <v>14394.36609441956</v>
+        <v>11678.01716583805</v>
       </c>
     </row>
     <row r="114">
@@ -5146,19 +2322,7 @@
         <v>49430</v>
       </c>
       <c r="B114" t="n">
-        <v>11492.0702757615</v>
-      </c>
-      <c r="C114" t="n">
-        <v>9274.188310941792</v>
-      </c>
-      <c r="D114" t="n">
-        <v>13709.9522405812</v>
-      </c>
-      <c r="E114" t="n">
-        <v>8095.938517131324</v>
-      </c>
-      <c r="F114" t="n">
-        <v>14888.20203439167</v>
+        <v>11542.86787573189</v>
       </c>
     </row>
     <row r="115">
@@ -5166,19 +2330,7 @@
         <v>49461</v>
       </c>
       <c r="B115" t="n">
-        <v>12161.10161055654</v>
-      </c>
-      <c r="C115" t="n">
-        <v>9943.219645736839</v>
-      </c>
-      <c r="D115" t="n">
-        <v>14378.98357537625</v>
-      </c>
-      <c r="E115" t="n">
-        <v>8764.969851926371</v>
-      </c>
-      <c r="F115" t="n">
-        <v>15557.23336918672</v>
+        <v>11753.13074533874</v>
       </c>
     </row>
     <row r="116">
@@ -5186,19 +2338,7 @@
         <v>49491</v>
       </c>
       <c r="B116" t="n">
-        <v>13702.45564063418</v>
-      </c>
-      <c r="C116" t="n">
-        <v>11484.57367581448</v>
-      </c>
-      <c r="D116" t="n">
-        <v>15920.33760545389</v>
-      </c>
-      <c r="E116" t="n">
-        <v>10306.32388200401</v>
-      </c>
-      <c r="F116" t="n">
-        <v>17098.58739926436</v>
+        <v>12275.45488389259</v>
       </c>
     </row>
     <row r="117">
@@ -5206,19 +2346,7 @@
         <v>49522</v>
       </c>
       <c r="B117" t="n">
-        <v>13903.16214745084</v>
-      </c>
-      <c r="C117" t="n">
-        <v>11685.28018263114</v>
-      </c>
-      <c r="D117" t="n">
-        <v>16121.04411227055</v>
-      </c>
-      <c r="E117" t="n">
-        <v>10507.03038882067</v>
-      </c>
-      <c r="F117" t="n">
-        <v>17299.29390608102</v>
+        <v>12409.6035844116</v>
       </c>
     </row>
     <row r="118">
@@ -5226,19 +2354,7 @@
         <v>49553</v>
       </c>
       <c r="B118" t="n">
-        <v>12270.18451672915</v>
-      </c>
-      <c r="C118" t="n">
-        <v>10052.30255190945</v>
-      </c>
-      <c r="D118" t="n">
-        <v>14488.06648154886</v>
-      </c>
-      <c r="E118" t="n">
-        <v>8874.05275809898</v>
-      </c>
-      <c r="F118" t="n">
-        <v>15666.31627535933</v>
+        <v>12288.5761555282</v>
       </c>
     </row>
     <row r="119">
@@ -5246,19 +2362,7 @@
         <v>49583</v>
       </c>
       <c r="B119" t="n">
-        <v>11846.84669486418</v>
-      </c>
-      <c r="C119" t="n">
-        <v>9628.964730044476</v>
-      </c>
-      <c r="D119" t="n">
-        <v>14064.72865968389</v>
-      </c>
-      <c r="E119" t="n">
-        <v>8450.714936234008</v>
-      </c>
-      <c r="F119" t="n">
-        <v>15242.97845349436</v>
+        <v>12308.61620889252</v>
       </c>
     </row>
     <row r="120">
@@ -5266,19 +2370,7 @@
         <v>49614</v>
       </c>
       <c r="B120" t="n">
-        <v>12169.70227520396</v>
-      </c>
-      <c r="C120" t="n">
-        <v>9951.820310384257</v>
-      </c>
-      <c r="D120" t="n">
-        <v>14387.58424002367</v>
-      </c>
-      <c r="E120" t="n">
-        <v>8773.570516573789</v>
-      </c>
-      <c r="F120" t="n">
-        <v>15565.83403383414</v>
+        <v>12098.39737553639</v>
       </c>
     </row>
     <row r="121">
@@ -5286,19 +2378,7 @@
         <v>49644</v>
       </c>
       <c r="B121" t="n">
-        <v>13473.85151381051</v>
-      </c>
-      <c r="C121" t="n">
-        <v>11255.9695489908</v>
-      </c>
-      <c r="D121" t="n">
-        <v>15691.73347863022</v>
-      </c>
-      <c r="E121" t="n">
-        <v>10077.71975518034</v>
-      </c>
-      <c r="F121" t="n">
-        <v>16869.98327244068</v>
+        <v>12270.80344811022</v>
       </c>
     </row>
   </sheetData>
